--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/شهریور کامل.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/شهریور کامل.xlsx
@@ -1,27 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27503"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\رسالت ابوالفضل\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A073E3E9-190C-4B21-89DB-3E4C6B5408AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42EB158-6E59-46A6-8B9F-CFB57F53C30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="785" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="209">
   <si>
     <t>صورت حساب سپرده</t>
   </si>
@@ -585,6 +598,69 @@
   </si>
   <si>
     <t>پست جدلی</t>
+  </si>
+  <si>
+    <t>بنزین برای کارگاه</t>
+  </si>
+  <si>
+    <t>اینترنت شرکت</t>
+  </si>
+  <si>
+    <t>تیپاکس کلیشه</t>
+  </si>
+  <si>
+    <t>آلبوم کاغذ دیواری</t>
+  </si>
+  <si>
+    <t>حلوا مسقطی</t>
+  </si>
+  <si>
+    <t>کلیشه طلعت مدنی</t>
+  </si>
+  <si>
+    <t>کارت تشکر</t>
+  </si>
+  <si>
+    <t>رضایی حمل بار</t>
+  </si>
+  <si>
+    <t>بازگشت وجه حلوا مسقطی حاج رسول</t>
+  </si>
+  <si>
+    <t>پماد سوختگی</t>
+  </si>
+  <si>
+    <t>بابت خرید باطری، ماژیک و میخ از کارت شخصیم</t>
+  </si>
+  <si>
+    <t>بلیط اتوبوس اصفهان</t>
+  </si>
+  <si>
+    <t>3 کیلو حلوا مسقطی فاخر</t>
+  </si>
+  <si>
+    <t>7 کیلو حلوا مسقطی فاخر</t>
+  </si>
+  <si>
+    <t>کارتن بسته بندی کوچک</t>
+  </si>
+  <si>
+    <t>اتوبوس شیراز</t>
+  </si>
+  <si>
+    <t>کاغذ a4</t>
+  </si>
+  <si>
+    <t>چسب پاک کن</t>
+  </si>
+  <si>
+    <t>بتنور سفر</t>
+  </si>
+  <si>
+    <t>سفر نمایشگاه</t>
+  </si>
+  <si>
+    <t>حمل بار نمایشگاه</t>
   </si>
 </sst>
 </file>
@@ -628,7 +704,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -677,6 +753,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -705,7 +799,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -724,22 +818,16 @@
     <xf numFmtId="3" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -766,7 +854,34 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -787,9 +902,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -827,7 +942,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -933,7 +1048,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1075,7 +1190,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1084,7 +1199,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I88"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
     <col min="2" max="3" width="14" customWidth="1"/>
@@ -1099,30 +1214,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
+      <c r="A1" s="18" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
     </row>
     <row r="2" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
+      <c r="E2" s="19"/>
+      <c r="F2" s="19"/>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
     </row>
     <row r="3" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
@@ -3590,17 +3705,17 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="7" t="s">
+      <c r="A88" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="B88" s="7"/>
-      <c r="C88" s="7"/>
-      <c r="D88" s="7"/>
-      <c r="E88" s="7"/>
-      <c r="F88" s="7"/>
-      <c r="G88" s="7"/>
-      <c r="H88" s="7"/>
-      <c r="I88" s="7"/>
+      <c r="B88" s="19"/>
+      <c r="C88" s="19"/>
+      <c r="D88" s="19"/>
+      <c r="E88" s="19"/>
+      <c r="F88" s="19"/>
+      <c r="G88" s="19"/>
+      <c r="H88" s="19"/>
+      <c r="I88" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3617,2946 +3732,3130 @@
   <dimension ref="A1:P85"/>
   <sheetFormatPr defaultRowHeight="24.75" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="5.5703125" style="9" customWidth="1"/>
-    <col min="2" max="4" width="11.5703125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="60.7109375" style="9" customWidth="1"/>
-    <col min="6" max="8" width="14.5703125" style="9" customWidth="1"/>
-    <col min="9" max="15" width="10.28515625" style="9" customWidth="1"/>
-    <col min="16" max="16" width="40.42578125" style="9" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="9"/>
+    <col min="1" max="1" width="5.5703125" style="7" customWidth="1"/>
+    <col min="2" max="4" width="11.5703125" style="7" customWidth="1"/>
+    <col min="5" max="5" width="63.140625" style="7" customWidth="1"/>
+    <col min="6" max="8" width="14.5703125" style="7" customWidth="1"/>
+    <col min="9" max="15" width="10.28515625" style="7" customWidth="1"/>
+    <col min="16" max="16" width="43.85546875" style="7" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="B1" s="8" t="s">
+      <c r="A1" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="E1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="I1" s="12" t="s">
+      <c r="I1" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="J1" s="12" t="s">
+      <c r="J1" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="K1" s="12" t="s">
+      <c r="K1" s="10" t="s">
         <v>181</v>
       </c>
-      <c r="L1" s="12" t="s">
+      <c r="L1" s="10" t="s">
         <v>182</v>
       </c>
-      <c r="M1" s="12" t="s">
+      <c r="M1" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="N1" s="12" t="s">
+      <c r="N1" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="O1" s="12" t="s">
+      <c r="O1" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="P1" s="13" t="s">
+      <c r="P1" s="11" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="15">
+      <c r="A2" s="13">
         <v>1</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" s="15" t="s">
+      <c r="B2" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="15" t="s">
+      <c r="E2" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="F2" s="16">
+      <c r="F2" s="14">
         <v>100000</v>
       </c>
-      <c r="G2" s="16">
-        <v>0</v>
-      </c>
-      <c r="H2" s="16">
+      <c r="G2" s="14">
+        <v>0</v>
+      </c>
+      <c r="H2" s="14">
         <v>17628096</v>
       </c>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
+      <c r="L2" s="15"/>
+      <c r="M2" s="15"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15"/>
     </row>
     <row r="3" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A3" s="15">
-        <v>2</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="A3" s="13">
+        <v>2</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="14">
         <v>9304000</v>
       </c>
-      <c r="G3" s="16">
-        <v>0</v>
-      </c>
-      <c r="H3" s="16">
+      <c r="G3" s="14">
+        <v>0</v>
+      </c>
+      <c r="H3" s="14">
         <v>8324096</v>
       </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
-      <c r="L3" s="17"/>
-      <c r="M3" s="17"/>
-      <c r="N3" s="17"/>
-      <c r="O3" s="17"/>
-      <c r="P3" s="17"/>
+      <c r="I3" s="15"/>
+      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="15"/>
+      <c r="M3" s="15"/>
+      <c r="N3" s="15"/>
+      <c r="O3" s="15"/>
+      <c r="P3" s="15"/>
     </row>
     <row r="4" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A4" s="10">
+      <c r="A4" s="8">
         <v>3</v>
       </c>
-      <c r="B4" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="10" t="s">
+      <c r="B4" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="11">
+      <c r="F4" s="9">
         <v>59000</v>
       </c>
-      <c r="G4" s="11">
-        <v>0</v>
-      </c>
-      <c r="H4" s="11">
+      <c r="G4" s="9">
+        <v>0</v>
+      </c>
+      <c r="H4" s="9">
         <v>8265096</v>
       </c>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="14"/>
-      <c r="M4" s="14"/>
-      <c r="N4" s="14"/>
-      <c r="O4" s="14"/>
-      <c r="P4" s="14"/>
+      <c r="I4" s="16">
+        <v>304</v>
+      </c>
+      <c r="J4" s="12"/>
+      <c r="K4" s="12"/>
+      <c r="L4" s="16">
+        <v>359</v>
+      </c>
+      <c r="M4" s="12"/>
+      <c r="N4" s="12"/>
+      <c r="O4" s="12"/>
+      <c r="P4" s="12" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A5" s="10">
+      <c r="A5" s="8">
         <v>4</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="10" t="s">
+      <c r="B5" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="10" t="s">
+      <c r="D5" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="11">
+      <c r="F5" s="9">
         <v>3300000</v>
       </c>
-      <c r="G5" s="11">
-        <v>0</v>
-      </c>
-      <c r="H5" s="11">
+      <c r="G5" s="9">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9">
         <v>4965096</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14"/>
-      <c r="M5" s="14"/>
-      <c r="N5" s="14"/>
-      <c r="O5" s="14"/>
-      <c r="P5" s="14"/>
+      <c r="I5" s="16">
+        <v>305</v>
+      </c>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="16">
+        <v>362</v>
+      </c>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A6" s="10">
+      <c r="A6" s="8">
         <v>5</v>
       </c>
-      <c r="B6" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="10" t="s">
+      <c r="B6" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="11">
-        <v>0</v>
-      </c>
-      <c r="G6" s="11">
+      <c r="F6" s="9">
+        <v>0</v>
+      </c>
+      <c r="G6" s="25">
         <v>49570000</v>
       </c>
-      <c r="H6" s="11">
+      <c r="H6" s="9">
         <v>54535096</v>
       </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="14"/>
-      <c r="M6" s="14"/>
-      <c r="N6" s="14"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="14"/>
+      <c r="I6" s="12"/>
+      <c r="J6" s="12"/>
+      <c r="K6" s="16">
+        <v>237</v>
+      </c>
+      <c r="L6" s="12"/>
+      <c r="M6" s="12"/>
+      <c r="N6" s="12"/>
+      <c r="O6" s="12"/>
+      <c r="P6" s="26"/>
     </row>
     <row r="7" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A7" s="10">
+      <c r="A7" s="8">
         <v>6</v>
       </c>
-      <c r="B7" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="10" t="s">
+      <c r="B7" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="11">
+      <c r="F7" s="9">
         <v>2381000</v>
       </c>
-      <c r="G7" s="11">
-        <v>0</v>
-      </c>
-      <c r="H7" s="11">
+      <c r="G7" s="9">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9">
         <v>52154096</v>
       </c>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="14"/>
-      <c r="M7" s="14"/>
-      <c r="N7" s="14"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="14"/>
+      <c r="I7" s="16">
+        <v>306</v>
+      </c>
+      <c r="J7" s="12"/>
+      <c r="K7" s="12"/>
+      <c r="L7" s="16">
+        <v>361</v>
+      </c>
+      <c r="M7" s="12"/>
+      <c r="N7" s="12"/>
+      <c r="O7" s="12"/>
+      <c r="P7" s="12" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A8" s="10">
+      <c r="A8" s="8">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C8" s="10" t="s">
+      <c r="B8" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="10" t="s">
+      <c r="D8" s="8" t="s">
         <v>29</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="11">
+      <c r="F8" s="9">
         <v>9000</v>
       </c>
-      <c r="G8" s="11">
-        <v>0</v>
-      </c>
-      <c r="H8" s="11">
+      <c r="G8" s="9">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9">
         <v>52145096</v>
       </c>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="14"/>
-      <c r="M8" s="18"/>
-      <c r="N8" s="18"/>
-      <c r="O8" s="18">
+      <c r="I8" s="12"/>
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+      <c r="M8" s="16"/>
+      <c r="N8" s="16"/>
+      <c r="O8" s="16">
         <v>9000</v>
       </c>
-      <c r="P8" s="14"/>
+      <c r="P8" s="12"/>
     </row>
     <row r="9" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A9" s="10">
+      <c r="A9" s="8">
         <v>8</v>
       </c>
-      <c r="B9" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C9" s="10" t="s">
+      <c r="B9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="10" t="s">
+      <c r="D9" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="11">
+      <c r="F9" s="9">
         <v>2500000</v>
       </c>
-      <c r="G9" s="11">
-        <v>0</v>
-      </c>
-      <c r="H9" s="11">
+      <c r="G9" s="9">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9">
         <v>49645096</v>
       </c>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="14"/>
-      <c r="M9" s="14"/>
-      <c r="N9" s="14"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="14"/>
+      <c r="I9" s="16">
+        <v>307</v>
+      </c>
+      <c r="J9" s="12"/>
+      <c r="K9" s="12"/>
+      <c r="L9" s="16">
+        <v>363</v>
+      </c>
+      <c r="M9" s="12"/>
+      <c r="N9" s="12"/>
+      <c r="O9" s="12"/>
+      <c r="P9" s="12" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A10" s="10">
+      <c r="A10" s="8">
         <v>9</v>
       </c>
-      <c r="B10" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C10" s="10" t="s">
+      <c r="B10" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="10" t="s">
+      <c r="D10" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="11">
+      <c r="F10" s="9">
         <v>9600000</v>
       </c>
-      <c r="G10" s="11">
-        <v>0</v>
-      </c>
-      <c r="H10" s="11">
+      <c r="G10" s="9">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9">
         <v>40045096</v>
       </c>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="14"/>
-      <c r="M10" s="14"/>
-      <c r="N10" s="14"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="14"/>
+      <c r="I10" s="16">
+        <v>308</v>
+      </c>
+      <c r="J10" s="12"/>
+      <c r="K10" s="12"/>
+      <c r="L10" s="16">
+        <v>364</v>
+      </c>
+      <c r="M10" s="12"/>
+      <c r="N10" s="12"/>
+      <c r="O10" s="12"/>
+      <c r="P10" s="12" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A11" s="10">
+      <c r="A11" s="8">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="10" t="s">
+      <c r="B11" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C11" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="D11" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="11">
+      <c r="F11" s="9">
         <v>18600</v>
       </c>
-      <c r="G11" s="11">
-        <v>0</v>
-      </c>
-      <c r="H11" s="11">
+      <c r="G11" s="9">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9">
         <v>40026496</v>
       </c>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
-      <c r="M11" s="18"/>
-      <c r="N11" s="18"/>
-      <c r="O11" s="18">
+      <c r="I11" s="12"/>
+      <c r="J11" s="12"/>
+      <c r="K11" s="12"/>
+      <c r="L11" s="12"/>
+      <c r="M11" s="16"/>
+      <c r="N11" s="16"/>
+      <c r="O11" s="16">
         <v>18600</v>
       </c>
-      <c r="P11" s="14"/>
+      <c r="P11" s="12"/>
     </row>
     <row r="12" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A12" s="10">
-        <v>11</v>
-      </c>
-      <c r="B12" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C12" s="10" t="s">
+      <c r="A12" s="8">
+        <v>11</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="10" t="s">
+      <c r="D12" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E12" s="10" t="s">
+      <c r="E12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="11">
+      <c r="F12" s="9">
         <v>35000000</v>
       </c>
-      <c r="G12" s="11">
-        <v>0</v>
-      </c>
-      <c r="H12" s="11">
+      <c r="G12" s="9">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9">
         <v>5026496</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="14"/>
-      <c r="M12" s="14"/>
-      <c r="N12" s="14"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="14"/>
+      <c r="I12" s="16">
+        <v>309</v>
+      </c>
+      <c r="J12" s="12"/>
+      <c r="K12" s="12"/>
+      <c r="L12" s="16">
+        <v>365</v>
+      </c>
+      <c r="M12" s="12"/>
+      <c r="N12" s="12"/>
+      <c r="O12" s="12"/>
+      <c r="P12" s="12" t="s">
+        <v>193</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A13" s="10">
+      <c r="A13" s="8">
         <v>12</v>
       </c>
-      <c r="B13" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C13" s="10" t="s">
+      <c r="B13" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C13" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="D13" s="10" t="s">
+      <c r="D13" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="E13" s="10" t="s">
+      <c r="E13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="11">
+      <c r="F13" s="9">
         <v>2250000</v>
       </c>
-      <c r="G13" s="11">
-        <v>0</v>
-      </c>
-      <c r="H13" s="11">
+      <c r="G13" s="9">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9">
         <v>2776496</v>
       </c>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="14"/>
-      <c r="N13" s="14"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="14"/>
+      <c r="I13" s="16">
+        <v>310</v>
+      </c>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="16">
+        <v>366</v>
+      </c>
+      <c r="M13" s="12"/>
+      <c r="N13" s="12"/>
+      <c r="O13" s="12"/>
+      <c r="P13" s="12" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A14" s="10">
+      <c r="A14" s="8">
         <v>13</v>
       </c>
-      <c r="B14" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="10" t="s">
+      <c r="B14" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C14" s="8" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="10" t="s">
+      <c r="D14" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="E14" s="10" t="s">
+      <c r="E14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="11">
+      <c r="F14" s="9">
         <v>2756000</v>
       </c>
-      <c r="G14" s="11">
-        <v>0</v>
-      </c>
-      <c r="H14" s="11">
+      <c r="G14" s="9">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9">
         <v>20496</v>
       </c>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="14"/>
-      <c r="N14" s="14"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="14"/>
+      <c r="I14" s="16">
+        <v>311</v>
+      </c>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="16">
+        <v>367</v>
+      </c>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A15" s="10">
+      <c r="A15" s="8">
         <v>14</v>
       </c>
-      <c r="B15" s="10" t="s">
+      <c r="B15" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="10" t="s">
+      <c r="D15" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="E15" s="10" t="s">
+      <c r="E15" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="F15" s="11">
-        <v>0</v>
-      </c>
-      <c r="G15" s="11">
+      <c r="F15" s="9">
+        <v>0</v>
+      </c>
+      <c r="G15" s="25">
         <v>60000000</v>
       </c>
-      <c r="H15" s="11">
+      <c r="H15" s="9">
         <v>60020496</v>
       </c>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="14"/>
-      <c r="N15" s="14"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="14"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="16">
+        <v>263</v>
+      </c>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="26"/>
     </row>
     <row r="16" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A16" s="10">
+      <c r="A16" s="8">
         <v>15</v>
       </c>
-      <c r="B16" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="10" t="s">
+      <c r="B16" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="D16" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="E16" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="F16" s="11">
-        <v>0</v>
-      </c>
-      <c r="G16" s="11">
+      <c r="F16" s="9">
+        <v>0</v>
+      </c>
+      <c r="G16" s="25">
         <v>150000000</v>
       </c>
-      <c r="H16" s="11">
+      <c r="H16" s="9">
         <v>210020496</v>
       </c>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="14"/>
-      <c r="N16" s="14"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="14"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="16">
+        <v>265</v>
+      </c>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="26"/>
     </row>
     <row r="17" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A17" s="10">
+      <c r="A17" s="8">
         <v>16</v>
       </c>
-      <c r="B17" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="10" t="s">
+      <c r="B17" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="D17" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="E17" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="11">
-        <v>0</v>
-      </c>
-      <c r="G17" s="11">
+      <c r="F17" s="9">
+        <v>0</v>
+      </c>
+      <c r="G17" s="25">
         <v>15300000</v>
       </c>
-      <c r="H17" s="11">
+      <c r="H17" s="9">
         <v>225320496</v>
       </c>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="14"/>
-      <c r="N17" s="14"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="14"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="16">
+        <v>264</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="26"/>
     </row>
     <row r="18" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A18" s="10">
+      <c r="A18" s="8">
         <v>17</v>
       </c>
-      <c r="B18" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="10" t="s">
+      <c r="B18" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="10" t="s">
+      <c r="D18" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="11">
+      <c r="F18" s="9">
         <v>53800</v>
       </c>
-      <c r="G18" s="11">
-        <v>0</v>
-      </c>
-      <c r="H18" s="11">
+      <c r="G18" s="9">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9">
         <v>225266696</v>
       </c>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="18"/>
-      <c r="N18" s="18"/>
-      <c r="O18" s="18">
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="16"/>
+      <c r="N18" s="16"/>
+      <c r="O18" s="16">
         <v>53800</v>
       </c>
-      <c r="P18" s="14"/>
+      <c r="P18" s="26"/>
     </row>
     <row r="19" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A19" s="10">
+      <c r="A19" s="8">
         <v>18</v>
       </c>
-      <c r="B19" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="10" t="s">
+      <c r="B19" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="10" t="s">
+      <c r="D19" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="10" t="s">
+      <c r="E19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="11">
+      <c r="F19" s="9">
         <v>150000000</v>
       </c>
-      <c r="G19" s="11">
-        <v>0</v>
-      </c>
-      <c r="H19" s="11">
+      <c r="G19" s="9">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9">
         <v>75266696</v>
       </c>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="14"/>
-      <c r="N19" s="14"/>
-      <c r="O19" s="14"/>
-      <c r="P19" s="14"/>
+      <c r="I19" s="16">
+        <v>312</v>
+      </c>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="16">
+        <v>368</v>
+      </c>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A20" s="10">
+      <c r="A20" s="8">
         <v>19</v>
       </c>
-      <c r="B20" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="10" t="s">
+      <c r="B20" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D20" s="10" t="s">
+      <c r="D20" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E20" s="10" t="s">
+      <c r="E20" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="11">
+      <c r="F20" s="9">
         <v>9000</v>
       </c>
-      <c r="G20" s="11">
-        <v>0</v>
-      </c>
-      <c r="H20" s="11">
+      <c r="G20" s="9">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9">
         <v>75257696</v>
       </c>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="18"/>
-      <c r="N20" s="18"/>
-      <c r="O20" s="18">
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="16"/>
+      <c r="N20" s="16"/>
+      <c r="O20" s="16">
         <v>9000</v>
       </c>
-      <c r="P20" s="14"/>
+      <c r="P20" s="12"/>
     </row>
     <row r="21" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A21" s="10">
+      <c r="A21" s="8">
         <v>20</v>
       </c>
-      <c r="B21" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="10" t="s">
+      <c r="B21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D21" s="10" t="s">
+      <c r="D21" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="E21" s="10" t="s">
+      <c r="E21" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F21" s="11">
+      <c r="F21" s="9">
         <v>1300000</v>
       </c>
-      <c r="G21" s="11">
-        <v>0</v>
-      </c>
-      <c r="H21" s="11">
+      <c r="G21" s="9">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9">
         <v>73957696</v>
       </c>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
+      <c r="I21" s="16">
+        <v>313</v>
+      </c>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="16">
+        <v>369</v>
+      </c>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12" t="s">
+        <v>198</v>
+      </c>
     </row>
     <row r="22" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A22" s="10">
+      <c r="A22" s="8">
         <v>21</v>
       </c>
-      <c r="B22" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="10" t="s">
+      <c r="B22" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="10" t="s">
+      <c r="D22" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E22" s="10" t="s">
+      <c r="E22" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="11">
+      <c r="F22" s="9">
         <v>9000</v>
       </c>
-      <c r="G22" s="11">
-        <v>0</v>
-      </c>
-      <c r="H22" s="11">
+      <c r="G22" s="9">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9">
         <v>73948696</v>
       </c>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="18"/>
-      <c r="N22" s="18"/>
-      <c r="O22" s="18">
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="16"/>
+      <c r="N22" s="16"/>
+      <c r="O22" s="16">
         <v>9000</v>
       </c>
-      <c r="P22" s="14"/>
+      <c r="P22" s="12"/>
     </row>
     <row r="23" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A23" s="10">
+      <c r="A23" s="8">
         <v>22</v>
       </c>
-      <c r="B23" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="10" t="s">
+      <c r="B23" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C23" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="D23" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="E23" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="11">
+      <c r="F23" s="9">
         <v>3000000</v>
       </c>
-      <c r="G23" s="11">
-        <v>0</v>
-      </c>
-      <c r="H23" s="11">
+      <c r="G23" s="9">
+        <v>0</v>
+      </c>
+      <c r="H23" s="9">
         <v>70948696</v>
       </c>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-      <c r="N23" s="14"/>
-      <c r="O23" s="14"/>
-      <c r="P23" s="14"/>
+      <c r="I23" s="16">
+        <v>314</v>
+      </c>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="16">
+        <v>370</v>
+      </c>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A24" s="10">
+      <c r="A24" s="8">
         <v>23</v>
       </c>
-      <c r="B24" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C24" s="10" t="s">
+      <c r="B24" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C24" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="D24" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="E24" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="11">
+      <c r="F24" s="9">
         <v>1630000</v>
       </c>
-      <c r="G24" s="11">
-        <v>0</v>
-      </c>
-      <c r="H24" s="11">
+      <c r="G24" s="9">
+        <v>0</v>
+      </c>
+      <c r="H24" s="9">
         <v>69318696</v>
       </c>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-      <c r="N24" s="14"/>
-      <c r="O24" s="14"/>
-      <c r="P24" s="14"/>
+      <c r="I24" s="16">
+        <v>315</v>
+      </c>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="16">
+        <v>371</v>
+      </c>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12" t="s">
+        <v>197</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="10">
+      <c r="A25" s="22">
         <v>24</v>
       </c>
-      <c r="B25" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="10" t="s">
+      <c r="B25" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="D25" s="22" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="E25" s="22" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="11">
+      <c r="F25" s="23">
         <v>14400000</v>
       </c>
-      <c r="G25" s="11">
-        <v>0</v>
-      </c>
-      <c r="H25" s="11">
+      <c r="G25" s="23">
+        <v>0</v>
+      </c>
+      <c r="H25" s="23">
         <v>54918696</v>
       </c>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="14"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="14"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="10">
+      <c r="A26" s="22">
         <v>25</v>
       </c>
-      <c r="B26" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="10" t="s">
+      <c r="B26" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="22" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="10" t="s">
+      <c r="D26" s="22" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="10" t="s">
+      <c r="E26" s="22" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="11">
+      <c r="F26" s="23">
         <v>33600000</v>
       </c>
-      <c r="G26" s="11">
-        <v>0</v>
-      </c>
-      <c r="H26" s="11">
+      <c r="G26" s="23">
+        <v>0</v>
+      </c>
+      <c r="H26" s="23">
         <v>21318696</v>
       </c>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-      <c r="N26" s="14"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="14"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A27" s="10">
+      <c r="A27" s="8">
         <v>26</v>
       </c>
-      <c r="B27" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C27" s="10" t="s">
+      <c r="B27" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C27" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="10" t="s">
+      <c r="D27" s="8" t="s">
         <v>67</v>
       </c>
-      <c r="E27" s="10" t="s">
+      <c r="E27" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="F27" s="11">
-        <v>0</v>
-      </c>
-      <c r="G27" s="11">
+      <c r="F27" s="9">
+        <v>0</v>
+      </c>
+      <c r="G27" s="21">
         <v>773900000</v>
       </c>
-      <c r="H27" s="11">
+      <c r="H27" s="9">
         <v>795218696</v>
       </c>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-      <c r="N27" s="14"/>
-      <c r="O27" s="14"/>
-      <c r="P27" s="14"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="20"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="20"/>
     </row>
     <row r="28" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A28" s="10">
+      <c r="A28" s="8">
         <v>27</v>
       </c>
-      <c r="B28" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C28" s="10" t="s">
+      <c r="B28" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C28" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D28" s="10" t="s">
+      <c r="D28" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E28" s="10" t="s">
+      <c r="E28" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="11">
+      <c r="F28" s="9">
         <v>25000</v>
       </c>
-      <c r="G28" s="11">
-        <v>0</v>
-      </c>
-      <c r="H28" s="11">
+      <c r="G28" s="9">
+        <v>0</v>
+      </c>
+      <c r="H28" s="9">
         <v>795193696</v>
       </c>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="18"/>
-      <c r="N28" s="18"/>
-      <c r="O28" s="18">
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="16"/>
+      <c r="N28" s="16"/>
+      <c r="O28" s="16">
         <v>25000</v>
       </c>
-      <c r="P28" s="14"/>
+      <c r="P28" s="12"/>
     </row>
     <row r="29" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A29" s="10">
+      <c r="A29" s="8">
         <v>28</v>
       </c>
-      <c r="B29" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C29" s="10" t="s">
+      <c r="B29" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C29" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D29" s="10" t="s">
+      <c r="D29" s="8" t="s">
         <v>69</v>
       </c>
-      <c r="E29" s="10" t="s">
+      <c r="E29" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F29" s="11">
+      <c r="F29" s="9">
         <v>50000000</v>
       </c>
-      <c r="G29" s="11">
-        <v>0</v>
-      </c>
-      <c r="H29" s="11">
+      <c r="G29" s="9">
+        <v>0</v>
+      </c>
+      <c r="H29" s="9">
         <v>745193696</v>
       </c>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-      <c r="N29" s="14"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="14"/>
+      <c r="I29" s="16">
+        <v>316</v>
+      </c>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="16">
+        <v>371</v>
+      </c>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="30" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A30" s="10">
+      <c r="A30" s="8">
         <v>29</v>
       </c>
-      <c r="B30" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C30" s="10" t="s">
+      <c r="B30" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="10" t="s">
+      <c r="D30" s="8" t="s">
         <v>72</v>
       </c>
-      <c r="E30" s="10" t="s">
+      <c r="E30" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F30" s="11">
+      <c r="F30" s="9">
         <v>23100000</v>
       </c>
-      <c r="G30" s="11">
-        <v>0</v>
-      </c>
-      <c r="H30" s="11">
+      <c r="G30" s="9">
+        <v>0</v>
+      </c>
+      <c r="H30" s="9">
         <v>722093696</v>
       </c>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-      <c r="N30" s="14"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="14"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="17" t="s">
+        <v>199</v>
+      </c>
     </row>
     <row r="31" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="10">
+      <c r="A31" s="8">
         <v>30</v>
       </c>
-      <c r="B31" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C31" s="10" t="s">
+      <c r="B31" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D31" s="10" t="s">
+      <c r="D31" s="8" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="10" t="s">
+      <c r="E31" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F31" s="11">
+      <c r="F31" s="9">
         <v>11000</v>
       </c>
-      <c r="G31" s="11">
-        <v>0</v>
-      </c>
-      <c r="H31" s="11">
+      <c r="G31" s="9">
+        <v>0</v>
+      </c>
+      <c r="H31" s="9">
         <v>722082696</v>
       </c>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="18"/>
-      <c r="N31" s="18"/>
-      <c r="O31" s="18">
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="16"/>
+      <c r="N31" s="16"/>
+      <c r="O31" s="16">
         <v>11000</v>
       </c>
-      <c r="P31" s="14"/>
+      <c r="P31" s="12"/>
     </row>
     <row r="32" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="10">
+      <c r="A32" s="8">
         <v>31</v>
       </c>
-      <c r="B32" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C32" s="10" t="s">
+      <c r="B32" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D32" s="10" t="s">
+      <c r="D32" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="E32" s="10" t="s">
+      <c r="E32" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="11">
+      <c r="F32" s="9">
         <v>2000000</v>
       </c>
-      <c r="G32" s="11">
-        <v>0</v>
-      </c>
-      <c r="H32" s="11">
+      <c r="G32" s="9">
+        <v>0</v>
+      </c>
+      <c r="H32" s="9">
         <v>720082696</v>
       </c>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-      <c r="N32" s="14"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="14"/>
+      <c r="I32" s="16">
+        <v>317</v>
+      </c>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="27"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="33" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="10">
+      <c r="A33" s="8">
         <v>32</v>
       </c>
-      <c r="B33" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C33" s="10" t="s">
+      <c r="B33" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="10" t="s">
+      <c r="D33" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="10" t="s">
+      <c r="E33" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F33" s="11">
+      <c r="F33" s="9">
         <v>21600000</v>
       </c>
-      <c r="G33" s="11">
-        <v>0</v>
-      </c>
-      <c r="H33" s="11">
+      <c r="G33" s="9">
+        <v>0</v>
+      </c>
+      <c r="H33" s="9">
         <v>698482696</v>
       </c>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-      <c r="N33" s="14"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="14"/>
+      <c r="I33" s="16"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="16"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="12"/>
+      <c r="P33" s="12" t="s">
+        <v>200</v>
+      </c>
     </row>
     <row r="34" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="10">
+      <c r="A34" s="8">
         <v>33</v>
       </c>
-      <c r="B34" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C34" s="10" t="s">
+      <c r="B34" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D34" s="10" t="s">
+      <c r="D34" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E34" s="10" t="s">
+      <c r="E34" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F34" s="11">
+      <c r="F34" s="9">
         <v>50400000</v>
       </c>
-      <c r="G34" s="11">
-        <v>0</v>
-      </c>
-      <c r="H34" s="11">
+      <c r="G34" s="9">
+        <v>0</v>
+      </c>
+      <c r="H34" s="9">
         <v>648082696</v>
       </c>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-      <c r="N34" s="14"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="14"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="12"/>
+      <c r="P34" s="17" t="s">
+        <v>201</v>
+      </c>
     </row>
     <row r="35" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="10">
+      <c r="A35" s="8">
         <v>34</v>
       </c>
-      <c r="B35" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C35" s="10" t="s">
+      <c r="B35" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D35" s="10" t="s">
+      <c r="D35" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E35" s="10" t="s">
+      <c r="E35" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="11">
+      <c r="F35" s="9">
         <v>14500</v>
       </c>
-      <c r="G35" s="11">
-        <v>0</v>
-      </c>
-      <c r="H35" s="11">
+      <c r="G35" s="9">
+        <v>0</v>
+      </c>
+      <c r="H35" s="9">
         <v>648068196</v>
       </c>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="18"/>
-      <c r="N35" s="18"/>
-      <c r="O35" s="18">
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="16"/>
+      <c r="N35" s="16"/>
+      <c r="O35" s="16">
         <v>14500</v>
       </c>
-      <c r="P35" s="14"/>
+      <c r="P35" s="12"/>
     </row>
     <row r="36" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="10">
+      <c r="A36" s="8">
         <v>35</v>
       </c>
-      <c r="B36" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C36" s="10" t="s">
+      <c r="B36" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>71</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="D36" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F36" s="11">
+      <c r="F36" s="9">
         <v>18000000</v>
       </c>
-      <c r="G36" s="11">
-        <v>0</v>
-      </c>
-      <c r="H36" s="11">
+      <c r="G36" s="9">
+        <v>0</v>
+      </c>
+      <c r="H36" s="9">
         <v>630068196</v>
       </c>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-      <c r="N36" s="14"/>
-      <c r="O36" s="14"/>
-      <c r="P36" s="14"/>
+      <c r="I36" s="16"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="16"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="12"/>
+      <c r="P36" s="12" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="37" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="10">
+      <c r="A37" s="22">
         <v>36</v>
       </c>
-      <c r="B37" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="10" t="s">
+      <c r="B37" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="10" t="s">
+      <c r="D37" s="22" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="10" t="s">
+      <c r="E37" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="F37" s="11">
-        <v>0</v>
-      </c>
-      <c r="G37" s="11">
+      <c r="F37" s="23">
+        <v>0</v>
+      </c>
+      <c r="G37" s="23">
         <v>48000000</v>
       </c>
-      <c r="H37" s="11">
+      <c r="H37" s="23">
         <v>678068196</v>
       </c>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-      <c r="K37" s="14"/>
-      <c r="L37" s="14"/>
-      <c r="M37" s="14"/>
-      <c r="N37" s="14"/>
-      <c r="O37" s="14"/>
-      <c r="P37" s="14"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="24" t="s">
+        <v>196</v>
+      </c>
     </row>
     <row r="38" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="10">
+      <c r="A38" s="8">
         <v>37</v>
       </c>
-      <c r="B38" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="10" t="s">
+      <c r="B38" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="10" t="s">
+      <c r="D38" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E38" s="10" t="s">
+      <c r="E38" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F38" s="11">
+      <c r="F38" s="9">
         <v>11400000</v>
       </c>
-      <c r="G38" s="11">
-        <v>0</v>
-      </c>
-      <c r="H38" s="11">
+      <c r="G38" s="9">
+        <v>0</v>
+      </c>
+      <c r="H38" s="9">
         <v>666668196</v>
       </c>
-      <c r="I38" s="14"/>
-      <c r="J38" s="14"/>
-      <c r="K38" s="14"/>
-      <c r="L38" s="14"/>
-      <c r="M38" s="14"/>
-      <c r="N38" s="14"/>
-      <c r="O38" s="14"/>
-      <c r="P38" s="14"/>
+      <c r="I38" s="16"/>
+      <c r="J38" s="12"/>
+      <c r="K38" s="12"/>
+      <c r="L38" s="16"/>
+      <c r="M38" s="12"/>
+      <c r="N38" s="12"/>
+      <c r="O38" s="12"/>
+      <c r="P38" s="12" t="s">
+        <v>204</v>
+      </c>
     </row>
     <row r="39" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="10">
+      <c r="A39" s="8">
         <v>38</v>
       </c>
-      <c r="B39" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="10" t="s">
+      <c r="B39" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="10" t="s">
+      <c r="D39" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E39" s="10" t="s">
+      <c r="E39" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F39" s="11">
+      <c r="F39" s="9">
         <v>11000</v>
       </c>
-      <c r="G39" s="11">
-        <v>0</v>
-      </c>
-      <c r="H39" s="11">
+      <c r="G39" s="9">
+        <v>0</v>
+      </c>
+      <c r="H39" s="9">
         <v>666657196</v>
       </c>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14"/>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14"/>
-      <c r="M39" s="18"/>
-      <c r="N39" s="18"/>
-      <c r="O39" s="18">
+      <c r="I39" s="12"/>
+      <c r="J39" s="12"/>
+      <c r="K39" s="12"/>
+      <c r="L39" s="12"/>
+      <c r="M39" s="16"/>
+      <c r="N39" s="16"/>
+      <c r="O39" s="16">
         <v>11000</v>
       </c>
-      <c r="P39" s="14"/>
+      <c r="P39" s="12"/>
     </row>
     <row r="40" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="10">
+      <c r="A40" s="8">
         <v>39</v>
       </c>
-      <c r="B40" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="10" t="s">
+      <c r="B40" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E40" s="10" t="s">
+      <c r="E40" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F40" s="11">
+      <c r="F40" s="9">
         <v>700000</v>
       </c>
-      <c r="G40" s="11">
-        <v>0</v>
-      </c>
-      <c r="H40" s="11">
+      <c r="G40" s="9">
+        <v>0</v>
+      </c>
+      <c r="H40" s="9">
         <v>665957196</v>
       </c>
-      <c r="I40" s="14"/>
-      <c r="J40" s="14"/>
-      <c r="K40" s="14"/>
-      <c r="L40" s="14"/>
-      <c r="M40" s="14"/>
-      <c r="N40" s="14"/>
-      <c r="O40" s="14"/>
-      <c r="P40" s="20"/>
+      <c r="I40" s="16"/>
+      <c r="J40" s="12"/>
+      <c r="K40" s="12"/>
+      <c r="L40" s="16"/>
+      <c r="M40" s="12"/>
+      <c r="N40" s="12"/>
+      <c r="O40" s="12"/>
+      <c r="P40" s="12" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="41" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A41" s="10">
+      <c r="A41" s="8">
         <v>40</v>
       </c>
-      <c r="B41" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="10" t="s">
+      <c r="B41" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E41" s="10" t="s">
+      <c r="E41" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F41" s="11">
+      <c r="F41" s="9">
         <v>8900000</v>
       </c>
-      <c r="G41" s="11">
-        <v>0</v>
-      </c>
-      <c r="H41" s="11">
+      <c r="G41" s="9">
+        <v>0</v>
+      </c>
+      <c r="H41" s="9">
         <v>657057196</v>
       </c>
-      <c r="I41" s="14"/>
-      <c r="J41" s="14"/>
-      <c r="K41" s="14"/>
-      <c r="L41" s="14"/>
-      <c r="M41" s="14"/>
-      <c r="N41" s="14"/>
-      <c r="O41" s="14"/>
-      <c r="P41" s="20"/>
+      <c r="I41" s="12"/>
+      <c r="J41" s="12"/>
+      <c r="K41" s="12"/>
+      <c r="L41" s="12"/>
+      <c r="M41" s="12"/>
+      <c r="N41" s="12"/>
+      <c r="O41" s="12"/>
+      <c r="P41" s="17" t="s">
+        <v>203</v>
+      </c>
     </row>
     <row r="42" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A42" s="10">
+      <c r="A42" s="8">
         <v>41</v>
       </c>
-      <c r="B42" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="10" t="s">
+      <c r="B42" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F42" s="11">
+      <c r="F42" s="9">
         <v>850000</v>
       </c>
-      <c r="G42" s="11">
-        <v>0</v>
-      </c>
-      <c r="H42" s="11">
+      <c r="G42" s="9">
+        <v>0</v>
+      </c>
+      <c r="H42" s="9">
         <v>656207196</v>
       </c>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
-      <c r="P42" s="20"/>
+      <c r="I42" s="16"/>
+      <c r="J42" s="12"/>
+      <c r="K42" s="12"/>
+      <c r="L42" s="16"/>
+      <c r="M42" s="12"/>
+      <c r="N42" s="12"/>
+      <c r="O42" s="12"/>
+      <c r="P42" s="12" t="s">
+        <v>205</v>
+      </c>
     </row>
     <row r="43" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A43" s="10">
+      <c r="A43" s="8">
         <v>42</v>
       </c>
-      <c r="B43" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="10" t="s">
+      <c r="B43" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E43" s="10" t="s">
+      <c r="E43" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="F43" s="11">
+      <c r="F43" s="9">
         <v>4080000</v>
       </c>
-      <c r="G43" s="11">
-        <v>0</v>
-      </c>
-      <c r="H43" s="11">
+      <c r="G43" s="9">
+        <v>0</v>
+      </c>
+      <c r="H43" s="9">
         <v>652127196</v>
       </c>
-      <c r="I43" s="14"/>
-      <c r="J43" s="14"/>
-      <c r="K43" s="14"/>
-      <c r="L43" s="14"/>
-      <c r="M43" s="14"/>
-      <c r="N43" s="14"/>
-      <c r="O43" s="14"/>
-      <c r="P43" s="20"/>
+      <c r="I43" s="12"/>
+      <c r="J43" s="12"/>
+      <c r="K43" s="12"/>
+      <c r="L43" s="12"/>
+      <c r="M43" s="12"/>
+      <c r="N43" s="12"/>
+      <c r="O43" s="12"/>
+      <c r="P43" s="17" t="s">
+        <v>206</v>
+      </c>
     </row>
     <row r="44" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A44" s="10">
+      <c r="A44" s="8">
         <v>43</v>
       </c>
-      <c r="B44" s="10" t="s">
+      <c r="B44" s="8" t="s">
         <v>44</v>
       </c>
-      <c r="C44" s="10" t="s">
+      <c r="C44" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="8" t="s">
         <v>96</v>
       </c>
-      <c r="E44" s="10" t="s">
+      <c r="E44" s="8" t="s">
         <v>97</v>
       </c>
-      <c r="F44" s="11">
-        <v>0</v>
-      </c>
-      <c r="G44" s="11">
+      <c r="F44" s="9">
+        <v>0</v>
+      </c>
+      <c r="G44" s="21">
         <v>104000000</v>
       </c>
-      <c r="H44" s="11">
+      <c r="H44" s="9">
         <v>756127196</v>
       </c>
-      <c r="I44" s="14"/>
-      <c r="J44" s="14"/>
-      <c r="K44" s="14"/>
-      <c r="L44" s="14"/>
-      <c r="M44" s="14"/>
-      <c r="N44" s="14"/>
-      <c r="O44" s="14"/>
+      <c r="I44" s="12"/>
+      <c r="J44" s="12"/>
+      <c r="K44" s="20"/>
+      <c r="L44" s="12"/>
+      <c r="M44" s="12"/>
+      <c r="N44" s="12"/>
+      <c r="O44" s="12"/>
       <c r="P44" s="20"/>
     </row>
     <row r="45" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A45" s="10">
+      <c r="A45" s="8">
         <v>44</v>
       </c>
-      <c r="B45" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C45" s="10" t="s">
+      <c r="B45" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="8" t="s">
         <v>98</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="F45" s="11">
+      <c r="F45" s="9">
         <v>670000</v>
       </c>
-      <c r="G45" s="11">
-        <v>0</v>
-      </c>
-      <c r="H45" s="11">
+      <c r="G45" s="9">
+        <v>0</v>
+      </c>
+      <c r="H45" s="9">
         <v>755457196</v>
       </c>
-      <c r="I45" s="14"/>
-      <c r="J45" s="14"/>
-      <c r="K45" s="14"/>
-      <c r="L45" s="14"/>
-      <c r="M45" s="14"/>
-      <c r="N45" s="14"/>
-      <c r="O45" s="14"/>
-      <c r="P45" s="19"/>
+      <c r="I45" s="12"/>
+      <c r="J45" s="12"/>
+      <c r="K45" s="12"/>
+      <c r="L45" s="12"/>
+      <c r="M45" s="12"/>
+      <c r="N45" s="12"/>
+      <c r="O45" s="12"/>
+      <c r="P45" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="46" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A46" s="10">
+      <c r="A46" s="8">
         <v>45</v>
       </c>
-      <c r="B46" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C46" s="10" t="s">
+      <c r="B46" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F46" s="11">
+      <c r="F46" s="9">
         <v>1000000</v>
       </c>
-      <c r="G46" s="11">
-        <v>0</v>
-      </c>
-      <c r="H46" s="11">
+      <c r="G46" s="9">
+        <v>0</v>
+      </c>
+      <c r="H46" s="9">
         <v>754457196</v>
       </c>
-      <c r="I46" s="14"/>
-      <c r="J46" s="14"/>
-      <c r="K46" s="14"/>
-      <c r="L46" s="14"/>
-      <c r="M46" s="14"/>
-      <c r="N46" s="14"/>
-      <c r="O46" s="14"/>
-      <c r="P46" s="19"/>
+      <c r="I46" s="12"/>
+      <c r="J46" s="12"/>
+      <c r="K46" s="12"/>
+      <c r="L46" s="12"/>
+      <c r="M46" s="12"/>
+      <c r="N46" s="12"/>
+      <c r="O46" s="12"/>
+      <c r="P46" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="47" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A47" s="10">
+      <c r="A47" s="8">
         <v>46</v>
       </c>
-      <c r="B47" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C47" s="10" t="s">
+      <c r="B47" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D47" s="10" t="s">
+      <c r="D47" s="8" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="10" t="s">
+      <c r="E47" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F47" s="11">
+      <c r="F47" s="9">
         <v>7750000</v>
       </c>
-      <c r="G47" s="11">
-        <v>0</v>
-      </c>
-      <c r="H47" s="11">
+      <c r="G47" s="9">
+        <v>0</v>
+      </c>
+      <c r="H47" s="9">
         <v>746707196</v>
       </c>
-      <c r="I47" s="14"/>
-      <c r="J47" s="14"/>
-      <c r="K47" s="14"/>
-      <c r="L47" s="14"/>
-      <c r="M47" s="14"/>
-      <c r="N47" s="14"/>
-      <c r="O47" s="14"/>
-      <c r="P47" s="19"/>
+      <c r="I47" s="12"/>
+      <c r="J47" s="12"/>
+      <c r="K47" s="12"/>
+      <c r="L47" s="12"/>
+      <c r="M47" s="12"/>
+      <c r="N47" s="12"/>
+      <c r="O47" s="12"/>
+      <c r="P47" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="48" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A48" s="10">
+      <c r="A48" s="8">
         <v>47</v>
       </c>
-      <c r="B48" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C48" s="10" t="s">
+      <c r="B48" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D48" s="10" t="s">
+      <c r="D48" s="8" t="s">
         <v>105</v>
       </c>
-      <c r="E48" s="10" t="s">
+      <c r="E48" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F48" s="11">
+      <c r="F48" s="9">
         <v>1230000</v>
       </c>
-      <c r="G48" s="11">
-        <v>0</v>
-      </c>
-      <c r="H48" s="11">
+      <c r="G48" s="9">
+        <v>0</v>
+      </c>
+      <c r="H48" s="9">
         <v>745477196</v>
       </c>
-      <c r="I48" s="14"/>
-      <c r="J48" s="14"/>
-      <c r="K48" s="14"/>
-      <c r="L48" s="14"/>
-      <c r="M48" s="14"/>
-      <c r="N48" s="14"/>
-      <c r="O48" s="14"/>
-      <c r="P48" s="19"/>
+      <c r="I48" s="12"/>
+      <c r="J48" s="12"/>
+      <c r="K48" s="12"/>
+      <c r="L48" s="12"/>
+      <c r="M48" s="12"/>
+      <c r="N48" s="12"/>
+      <c r="O48" s="12"/>
+      <c r="P48" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="49" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A49" s="10">
+      <c r="A49" s="8">
         <v>48</v>
       </c>
-      <c r="B49" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C49" s="10" t="s">
+      <c r="B49" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D49" s="10" t="s">
+      <c r="D49" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="E49" s="10" t="s">
+      <c r="E49" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F49" s="11">
+      <c r="F49" s="9">
         <v>19085000</v>
       </c>
-      <c r="G49" s="11">
-        <v>0</v>
-      </c>
-      <c r="H49" s="11">
+      <c r="G49" s="9">
+        <v>0</v>
+      </c>
+      <c r="H49" s="9">
         <v>726392196</v>
       </c>
-      <c r="I49" s="14"/>
-      <c r="J49" s="14"/>
-      <c r="K49" s="14"/>
-      <c r="L49" s="14"/>
-      <c r="M49" s="14"/>
-      <c r="N49" s="14"/>
-      <c r="O49" s="14"/>
-      <c r="P49" s="19"/>
+      <c r="I49" s="12"/>
+      <c r="J49" s="12"/>
+      <c r="K49" s="12"/>
+      <c r="L49" s="12"/>
+      <c r="M49" s="12"/>
+      <c r="N49" s="12"/>
+      <c r="O49" s="12"/>
+      <c r="P49" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="50" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A50" s="10">
+      <c r="A50" s="8">
         <v>49</v>
       </c>
-      <c r="B50" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C50" s="10" t="s">
+      <c r="B50" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D50" s="10" t="s">
+      <c r="D50" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E50" s="10" t="s">
+      <c r="E50" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F50" s="11">
+      <c r="F50" s="9">
         <v>11000</v>
       </c>
-      <c r="G50" s="11">
-        <v>0</v>
-      </c>
-      <c r="H50" s="11">
+      <c r="G50" s="9">
+        <v>0</v>
+      </c>
+      <c r="H50" s="9">
         <v>726381196</v>
       </c>
-      <c r="I50" s="14"/>
-      <c r="J50" s="14"/>
-      <c r="K50" s="14"/>
-      <c r="L50" s="14"/>
-      <c r="M50" s="18"/>
-      <c r="N50" s="18"/>
-      <c r="O50" s="18">
+      <c r="I50" s="12"/>
+      <c r="J50" s="12"/>
+      <c r="K50" s="12"/>
+      <c r="L50" s="12"/>
+      <c r="M50" s="16"/>
+      <c r="N50" s="16"/>
+      <c r="O50" s="16">
         <v>11000</v>
       </c>
-      <c r="P50" s="14"/>
+      <c r="P50" s="12"/>
     </row>
     <row r="51" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A51" s="10">
+      <c r="A51" s="8">
         <v>50</v>
       </c>
-      <c r="B51" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C51" s="10" t="s">
+      <c r="B51" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D51" s="10" t="s">
+      <c r="D51" s="8" t="s">
         <v>109</v>
       </c>
-      <c r="E51" s="10" t="s">
+      <c r="E51" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="F51" s="11">
+      <c r="F51" s="9">
         <v>2620000</v>
       </c>
-      <c r="G51" s="11">
-        <v>0</v>
-      </c>
-      <c r="H51" s="11">
+      <c r="G51" s="9">
+        <v>0</v>
+      </c>
+      <c r="H51" s="9">
         <v>723761196</v>
       </c>
-      <c r="I51" s="14"/>
-      <c r="J51" s="14"/>
-      <c r="K51" s="14"/>
-      <c r="L51" s="14"/>
-      <c r="M51" s="14"/>
-      <c r="N51" s="14"/>
-      <c r="O51" s="14"/>
-      <c r="P51" s="14"/>
+      <c r="I51" s="12"/>
+      <c r="J51" s="12"/>
+      <c r="K51" s="12"/>
+      <c r="L51" s="12"/>
+      <c r="M51" s="12"/>
+      <c r="N51" s="12"/>
+      <c r="O51" s="12"/>
+      <c r="P51" s="12"/>
     </row>
     <row r="52" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A52" s="10">
+      <c r="A52" s="8">
         <v>51</v>
       </c>
-      <c r="B52" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C52" s="10" t="s">
+      <c r="B52" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D52" s="10" t="s">
+      <c r="D52" s="8" t="s">
         <v>111</v>
       </c>
-      <c r="E52" s="10" t="s">
+      <c r="E52" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F52" s="11">
+      <c r="F52" s="9">
         <v>2000000</v>
       </c>
-      <c r="G52" s="11">
-        <v>0</v>
-      </c>
-      <c r="H52" s="11">
+      <c r="G52" s="9">
+        <v>0</v>
+      </c>
+      <c r="H52" s="9">
         <v>721761196</v>
       </c>
-      <c r="I52" s="14"/>
-      <c r="J52" s="14"/>
-      <c r="K52" s="14"/>
-      <c r="L52" s="14"/>
-      <c r="M52" s="14"/>
-      <c r="N52" s="14"/>
-      <c r="O52" s="14"/>
-      <c r="P52" s="19"/>
+      <c r="I52" s="12"/>
+      <c r="J52" s="12"/>
+      <c r="K52" s="12"/>
+      <c r="L52" s="12"/>
+      <c r="M52" s="12"/>
+      <c r="N52" s="12"/>
+      <c r="O52" s="12"/>
+      <c r="P52" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="53" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A53" s="10">
+      <c r="A53" s="8">
         <v>52</v>
       </c>
-      <c r="B53" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C53" s="10" t="s">
+      <c r="B53" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="D53" s="10" t="s">
+      <c r="D53" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="E53" s="10" t="s">
+      <c r="E53" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F53" s="11">
+      <c r="F53" s="9">
         <v>10220000</v>
       </c>
-      <c r="G53" s="11">
-        <v>0</v>
-      </c>
-      <c r="H53" s="11">
+      <c r="G53" s="9">
+        <v>0</v>
+      </c>
+      <c r="H53" s="9">
         <v>711541196</v>
       </c>
-      <c r="I53" s="14"/>
-      <c r="J53" s="14"/>
-      <c r="K53" s="14"/>
-      <c r="L53" s="14"/>
-      <c r="M53" s="14"/>
-      <c r="N53" s="14"/>
-      <c r="O53" s="14"/>
-      <c r="P53" s="19"/>
+      <c r="I53" s="12"/>
+      <c r="J53" s="12"/>
+      <c r="K53" s="12"/>
+      <c r="L53" s="12"/>
+      <c r="M53" s="12"/>
+      <c r="N53" s="12"/>
+      <c r="O53" s="12"/>
+      <c r="P53" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="54" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A54" s="10">
+      <c r="A54" s="8">
         <v>53</v>
       </c>
-      <c r="B54" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C54" s="10" t="s">
+      <c r="B54" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D54" s="10" t="s">
+      <c r="D54" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="E54" s="10" t="s">
+      <c r="E54" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="F54" s="11">
+      <c r="F54" s="9">
         <v>2720000</v>
       </c>
-      <c r="G54" s="11">
-        <v>0</v>
-      </c>
-      <c r="H54" s="11">
+      <c r="G54" s="9">
+        <v>0</v>
+      </c>
+      <c r="H54" s="9">
         <v>708821196</v>
       </c>
-      <c r="I54" s="14"/>
-      <c r="J54" s="14"/>
-      <c r="K54" s="14"/>
-      <c r="L54" s="14"/>
-      <c r="M54" s="14"/>
-      <c r="N54" s="14"/>
-      <c r="O54" s="14"/>
-      <c r="P54" s="19"/>
+      <c r="I54" s="12"/>
+      <c r="J54" s="12"/>
+      <c r="K54" s="12"/>
+      <c r="L54" s="12"/>
+      <c r="M54" s="12"/>
+      <c r="N54" s="12"/>
+      <c r="O54" s="12"/>
+      <c r="P54" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="55" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A55" s="10">
+      <c r="A55" s="8">
         <v>54</v>
       </c>
-      <c r="B55" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C55" s="10" t="s">
+      <c r="B55" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D55" s="10" t="s">
+      <c r="D55" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="E55" s="10" t="s">
+      <c r="E55" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="F55" s="11">
+      <c r="F55" s="9">
         <v>1090000</v>
       </c>
-      <c r="G55" s="11">
-        <v>0</v>
-      </c>
-      <c r="H55" s="11">
+      <c r="G55" s="9">
+        <v>0</v>
+      </c>
+      <c r="H55" s="9">
         <v>707731196</v>
       </c>
-      <c r="I55" s="14"/>
-      <c r="J55" s="14"/>
-      <c r="K55" s="14"/>
-      <c r="L55" s="14"/>
-      <c r="M55" s="14"/>
-      <c r="N55" s="14"/>
-      <c r="O55" s="14"/>
-      <c r="P55" s="19"/>
+      <c r="I55" s="12"/>
+      <c r="J55" s="12"/>
+      <c r="K55" s="12"/>
+      <c r="L55" s="12"/>
+      <c r="M55" s="12"/>
+      <c r="N55" s="12"/>
+      <c r="O55" s="12"/>
+      <c r="P55" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="56" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A56" s="10">
+      <c r="A56" s="8">
         <v>55</v>
       </c>
-      <c r="B56" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C56" s="10" t="s">
+      <c r="B56" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D56" s="10" t="s">
+      <c r="D56" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E56" s="10" t="s">
+      <c r="E56" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F56" s="11">
+      <c r="F56" s="9">
         <v>60000</v>
       </c>
-      <c r="G56" s="11">
-        <v>0</v>
-      </c>
-      <c r="H56" s="11">
+      <c r="G56" s="9">
+        <v>0</v>
+      </c>
+      <c r="H56" s="9">
         <v>707671196</v>
       </c>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14"/>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14"/>
-      <c r="M56" s="18"/>
-      <c r="N56" s="18"/>
-      <c r="O56" s="18">
+      <c r="I56" s="12"/>
+      <c r="J56" s="12"/>
+      <c r="K56" s="12"/>
+      <c r="L56" s="12"/>
+      <c r="M56" s="16"/>
+      <c r="N56" s="16"/>
+      <c r="O56" s="16">
         <v>60000</v>
       </c>
-      <c r="P56" s="14"/>
+      <c r="P56" s="12"/>
     </row>
     <row r="57" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A57" s="10">
+      <c r="A57" s="8">
         <v>56</v>
       </c>
-      <c r="B57" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C57" s="10" t="s">
+      <c r="B57" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D57" s="10" t="s">
+      <c r="D57" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="E57" s="10" t="s">
+      <c r="E57" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F57" s="11">
+      <c r="F57" s="9">
         <v>150000000</v>
       </c>
-      <c r="G57" s="11">
-        <v>0</v>
-      </c>
-      <c r="H57" s="11">
+      <c r="G57" s="9">
+        <v>0</v>
+      </c>
+      <c r="H57" s="9">
         <v>557671196</v>
       </c>
-      <c r="I57" s="14"/>
-      <c r="J57" s="14"/>
-      <c r="K57" s="14"/>
-      <c r="L57" s="14"/>
-      <c r="M57" s="14"/>
-      <c r="N57" s="14"/>
-      <c r="O57" s="14"/>
-      <c r="P57" s="14"/>
+      <c r="I57" s="12"/>
+      <c r="J57" s="12"/>
+      <c r="K57" s="12"/>
+      <c r="L57" s="12"/>
+      <c r="M57" s="12"/>
+      <c r="N57" s="12"/>
+      <c r="O57" s="12"/>
+      <c r="P57" s="17" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="58" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A58" s="10">
+      <c r="A58" s="8">
         <v>57</v>
       </c>
-      <c r="B58" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C58" s="10" t="s">
+      <c r="B58" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D58" s="10" t="s">
+      <c r="D58" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="E58" s="10" t="s">
+      <c r="E58" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="F58" s="11">
+      <c r="F58" s="9">
         <v>2500000</v>
       </c>
-      <c r="G58" s="11">
-        <v>0</v>
-      </c>
-      <c r="H58" s="11">
+      <c r="G58" s="9">
+        <v>0</v>
+      </c>
+      <c r="H58" s="9">
         <v>555171196</v>
       </c>
-      <c r="I58" s="14"/>
-      <c r="J58" s="14"/>
-      <c r="K58" s="14"/>
-      <c r="L58" s="14"/>
-      <c r="M58" s="14"/>
-      <c r="N58" s="14"/>
-      <c r="O58" s="14"/>
-      <c r="P58" s="19"/>
+      <c r="I58" s="12"/>
+      <c r="J58" s="12"/>
+      <c r="K58" s="12"/>
+      <c r="L58" s="12"/>
+      <c r="M58" s="12"/>
+      <c r="N58" s="12"/>
+      <c r="O58" s="12"/>
+      <c r="P58" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="59" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A59" s="10">
+      <c r="A59" s="8">
         <v>58</v>
       </c>
-      <c r="B59" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C59" s="10" t="s">
+      <c r="B59" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D59" s="10" t="s">
+      <c r="D59" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="E59" s="10" t="s">
+      <c r="E59" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="F59" s="11">
+      <c r="F59" s="9">
         <v>1070000</v>
       </c>
-      <c r="G59" s="11">
-        <v>0</v>
-      </c>
-      <c r="H59" s="11">
+      <c r="G59" s="9">
+        <v>0</v>
+      </c>
+      <c r="H59" s="9">
         <v>554101196</v>
       </c>
-      <c r="I59" s="14"/>
-      <c r="J59" s="14"/>
-      <c r="K59" s="14"/>
-      <c r="L59" s="14"/>
-      <c r="M59" s="14"/>
-      <c r="N59" s="14"/>
-      <c r="O59" s="14"/>
-      <c r="P59" s="19"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+      <c r="L59" s="12"/>
+      <c r="M59" s="12"/>
+      <c r="N59" s="12"/>
+      <c r="O59" s="12"/>
+      <c r="P59" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="60" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A60" s="10">
+      <c r="A60" s="8">
         <v>59</v>
       </c>
-      <c r="B60" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C60" s="10" t="s">
+      <c r="B60" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D60" s="10" t="s">
+      <c r="D60" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="E60" s="10" t="s">
+      <c r="E60" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="F60" s="11">
+      <c r="F60" s="9">
         <v>9620000</v>
       </c>
-      <c r="G60" s="11">
-        <v>0</v>
-      </c>
-      <c r="H60" s="11">
+      <c r="G60" s="9">
+        <v>0</v>
+      </c>
+      <c r="H60" s="9">
         <v>544481196</v>
       </c>
-      <c r="I60" s="14"/>
-      <c r="J60" s="14"/>
-      <c r="K60" s="14"/>
-      <c r="L60" s="14"/>
-      <c r="M60" s="14"/>
-      <c r="N60" s="14"/>
-      <c r="O60" s="14"/>
-      <c r="P60" s="19"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="12"/>
+      <c r="M60" s="12"/>
+      <c r="N60" s="12"/>
+      <c r="O60" s="12"/>
+      <c r="P60" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="61" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A61" s="10">
+      <c r="A61" s="8">
         <v>60</v>
       </c>
-      <c r="B61" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C61" s="10" t="s">
+      <c r="B61" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D61" s="10" t="s">
+      <c r="D61" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="E61" s="10" t="s">
+      <c r="E61" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="F61" s="11">
+      <c r="F61" s="9">
         <v>1270000</v>
       </c>
-      <c r="G61" s="11">
-        <v>0</v>
-      </c>
-      <c r="H61" s="11">
+      <c r="G61" s="9">
+        <v>0</v>
+      </c>
+      <c r="H61" s="9">
         <v>543211196</v>
       </c>
-      <c r="I61" s="14"/>
-      <c r="J61" s="14"/>
-      <c r="K61" s="14"/>
-      <c r="L61" s="14"/>
-      <c r="M61" s="14"/>
-      <c r="N61" s="14"/>
-      <c r="O61" s="14"/>
-      <c r="P61" s="19"/>
+      <c r="I61" s="12"/>
+      <c r="J61" s="12"/>
+      <c r="K61" s="12"/>
+      <c r="L61" s="12"/>
+      <c r="M61" s="12"/>
+      <c r="N61" s="12"/>
+      <c r="O61" s="12"/>
+      <c r="P61" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="62" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A62" s="10">
+      <c r="A62" s="8">
         <v>61</v>
       </c>
-      <c r="B62" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C62" s="10" t="s">
+      <c r="B62" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D62" s="10" t="s">
+      <c r="D62" s="8" t="s">
         <v>130</v>
       </c>
-      <c r="E62" s="10" t="s">
+      <c r="E62" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="F62" s="11">
+      <c r="F62" s="9">
         <v>1500000</v>
       </c>
-      <c r="G62" s="11">
-        <v>0</v>
-      </c>
-      <c r="H62" s="11">
+      <c r="G62" s="9">
+        <v>0</v>
+      </c>
+      <c r="H62" s="9">
         <v>541711196</v>
       </c>
-      <c r="I62" s="14"/>
-      <c r="J62" s="14"/>
-      <c r="K62" s="14"/>
-      <c r="L62" s="14"/>
-      <c r="M62" s="14"/>
-      <c r="N62" s="14"/>
-      <c r="O62" s="14"/>
-      <c r="P62" s="19"/>
+      <c r="I62" s="12"/>
+      <c r="J62" s="12"/>
+      <c r="K62" s="12"/>
+      <c r="L62" s="12"/>
+      <c r="M62" s="12"/>
+      <c r="N62" s="12"/>
+      <c r="O62" s="12"/>
+      <c r="P62" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="63" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A63" s="10">
+      <c r="A63" s="8">
         <v>62</v>
       </c>
-      <c r="B63" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C63" s="10" t="s">
+      <c r="B63" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="D63" s="10" t="s">
+      <c r="D63" s="8" t="s">
         <v>132</v>
       </c>
-      <c r="E63" s="10" t="s">
+      <c r="E63" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="F63" s="11">
+      <c r="F63" s="9">
         <v>1040000</v>
       </c>
-      <c r="G63" s="11">
-        <v>0</v>
-      </c>
-      <c r="H63" s="11">
+      <c r="G63" s="9">
+        <v>0</v>
+      </c>
+      <c r="H63" s="9">
         <v>540671196</v>
       </c>
-      <c r="I63" s="14"/>
-      <c r="J63" s="14"/>
-      <c r="K63" s="14"/>
-      <c r="L63" s="14"/>
-      <c r="M63" s="14"/>
-      <c r="N63" s="14"/>
-      <c r="O63" s="14"/>
-      <c r="P63" s="19"/>
+      <c r="I63" s="12"/>
+      <c r="J63" s="12"/>
+      <c r="K63" s="12"/>
+      <c r="L63" s="12"/>
+      <c r="M63" s="12"/>
+      <c r="N63" s="12"/>
+      <c r="O63" s="12"/>
+      <c r="P63" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="64" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A64" s="10">
+      <c r="A64" s="8">
         <v>63</v>
       </c>
-      <c r="B64" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C64" s="10" t="s">
+      <c r="B64" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D64" s="10" t="s">
+      <c r="D64" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="E64" s="10" t="s">
+      <c r="E64" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F64" s="11">
+      <c r="F64" s="9">
         <v>11000</v>
       </c>
-      <c r="G64" s="11">
-        <v>0</v>
-      </c>
-      <c r="H64" s="11">
+      <c r="G64" s="9">
+        <v>0</v>
+      </c>
+      <c r="H64" s="9">
         <v>540660196</v>
       </c>
-      <c r="I64" s="14"/>
-      <c r="J64" s="14"/>
-      <c r="K64" s="14"/>
-      <c r="L64" s="14"/>
-      <c r="M64" s="18"/>
-      <c r="N64" s="18"/>
-      <c r="O64" s="18">
+      <c r="I64" s="12"/>
+      <c r="J64" s="12"/>
+      <c r="K64" s="12"/>
+      <c r="L64" s="12"/>
+      <c r="M64" s="16"/>
+      <c r="N64" s="16"/>
+      <c r="O64" s="16">
         <v>11000</v>
       </c>
-      <c r="P64" s="14"/>
+      <c r="P64" s="12"/>
     </row>
     <row r="65" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A65" s="10">
+      <c r="A65" s="8">
         <v>64</v>
       </c>
-      <c r="B65" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C65" s="10" t="s">
+      <c r="B65" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D65" s="10" t="s">
+      <c r="D65" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="E65" s="10" t="s">
+      <c r="E65" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F65" s="11">
+      <c r="F65" s="9">
         <v>2381000</v>
       </c>
-      <c r="G65" s="11">
-        <v>0</v>
-      </c>
-      <c r="H65" s="11">
+      <c r="G65" s="9">
+        <v>0</v>
+      </c>
+      <c r="H65" s="9">
         <v>538279196</v>
       </c>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
-      <c r="N65" s="14"/>
-      <c r="O65" s="14"/>
-      <c r="P65" s="14"/>
+      <c r="I65" s="12"/>
+      <c r="J65" s="12"/>
+      <c r="K65" s="12"/>
+      <c r="L65" s="12"/>
+      <c r="M65" s="12"/>
+      <c r="N65" s="12"/>
+      <c r="O65" s="12"/>
+      <c r="P65" s="12" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="66" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A66" s="10">
+      <c r="A66" s="8">
         <v>65</v>
       </c>
-      <c r="B66" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C66" s="10" t="s">
+      <c r="B66" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D66" s="10" t="s">
+      <c r="D66" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="E66" s="10" t="s">
+      <c r="E66" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="F66" s="11">
+      <c r="F66" s="9">
         <v>7500000</v>
       </c>
-      <c r="G66" s="11">
-        <v>0</v>
-      </c>
-      <c r="H66" s="11">
+      <c r="G66" s="9">
+        <v>0</v>
+      </c>
+      <c r="H66" s="9">
         <v>530779196</v>
       </c>
-      <c r="I66" s="14"/>
-      <c r="J66" s="14"/>
-      <c r="K66" s="14"/>
-      <c r="L66" s="14"/>
-      <c r="M66" s="14"/>
-      <c r="N66" s="14"/>
-      <c r="O66" s="14"/>
-      <c r="P66" s="19"/>
+      <c r="I66" s="12"/>
+      <c r="J66" s="12"/>
+      <c r="K66" s="12"/>
+      <c r="L66" s="12"/>
+      <c r="M66" s="12"/>
+      <c r="N66" s="12"/>
+      <c r="O66" s="12"/>
+      <c r="P66" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="67" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A67" s="10">
+      <c r="A67" s="8">
         <v>66</v>
       </c>
-      <c r="B67" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C67" s="10" t="s">
+      <c r="B67" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D67" s="10" t="s">
+      <c r="D67" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="E67" s="10" t="s">
+      <c r="E67" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F67" s="11">
+      <c r="F67" s="9">
         <v>1700000</v>
       </c>
-      <c r="G67" s="11">
-        <v>0</v>
-      </c>
-      <c r="H67" s="11">
+      <c r="G67" s="9">
+        <v>0</v>
+      </c>
+      <c r="H67" s="9">
         <v>529079196</v>
       </c>
-      <c r="I67" s="14"/>
-      <c r="J67" s="14"/>
-      <c r="K67" s="14"/>
-      <c r="L67" s="14"/>
-      <c r="M67" s="14"/>
-      <c r="N67" s="14"/>
-      <c r="O67" s="14"/>
-      <c r="P67" s="19"/>
+      <c r="I67" s="12"/>
+      <c r="J67" s="12"/>
+      <c r="K67" s="12"/>
+      <c r="L67" s="12"/>
+      <c r="M67" s="12"/>
+      <c r="N67" s="12"/>
+      <c r="O67" s="12"/>
+      <c r="P67" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="68" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A68" s="10">
+      <c r="A68" s="8">
         <v>67</v>
       </c>
-      <c r="B68" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C68" s="10" t="s">
+      <c r="B68" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D68" s="10" t="s">
+      <c r="D68" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E68" s="10" t="s">
+      <c r="E68" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="F68" s="11">
+      <c r="F68" s="9">
         <v>2330000</v>
       </c>
-      <c r="G68" s="11">
-        <v>0</v>
-      </c>
-      <c r="H68" s="11">
+      <c r="G68" s="9">
+        <v>0</v>
+      </c>
+      <c r="H68" s="9">
         <v>526749196</v>
       </c>
-      <c r="I68" s="14"/>
-      <c r="J68" s="14"/>
-      <c r="K68" s="14"/>
-      <c r="L68" s="14"/>
-      <c r="M68" s="14"/>
-      <c r="N68" s="14"/>
-      <c r="O68" s="14"/>
-      <c r="P68" s="19"/>
+      <c r="I68" s="12"/>
+      <c r="J68" s="12"/>
+      <c r="K68" s="12"/>
+      <c r="L68" s="12"/>
+      <c r="M68" s="12"/>
+      <c r="N68" s="12"/>
+      <c r="O68" s="12"/>
+      <c r="P68" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="69" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A69" s="10">
+      <c r="A69" s="8">
         <v>68</v>
       </c>
-      <c r="B69" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C69" s="10" t="s">
+      <c r="B69" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C69" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D69" s="10" t="s">
+      <c r="D69" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="E69" s="10" t="s">
+      <c r="E69" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="F69" s="11">
+      <c r="F69" s="9">
         <v>5590000</v>
       </c>
-      <c r="G69" s="11">
-        <v>0</v>
-      </c>
-      <c r="H69" s="11">
+      <c r="G69" s="9">
+        <v>0</v>
+      </c>
+      <c r="H69" s="9">
         <v>521159196</v>
       </c>
-      <c r="I69" s="14"/>
-      <c r="J69" s="14"/>
-      <c r="K69" s="14"/>
-      <c r="L69" s="14"/>
-      <c r="M69" s="14"/>
-      <c r="N69" s="14"/>
-      <c r="O69" s="14"/>
-      <c r="P69" s="19"/>
+      <c r="I69" s="12"/>
+      <c r="J69" s="12"/>
+      <c r="K69" s="12"/>
+      <c r="L69" s="12"/>
+      <c r="M69" s="12"/>
+      <c r="N69" s="12"/>
+      <c r="O69" s="12"/>
+      <c r="P69" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="70" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A70" s="10">
+      <c r="A70" s="8">
         <v>69</v>
       </c>
-      <c r="B70" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C70" s="10" t="s">
+      <c r="B70" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D70" s="10" t="s">
+      <c r="D70" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="E70" s="10" t="s">
+      <c r="E70" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="F70" s="11">
+      <c r="F70" s="9">
         <v>1050000</v>
       </c>
-      <c r="G70" s="11">
-        <v>0</v>
-      </c>
-      <c r="H70" s="11">
+      <c r="G70" s="9">
+        <v>0</v>
+      </c>
+      <c r="H70" s="9">
         <v>520109196</v>
       </c>
-      <c r="I70" s="14"/>
-      <c r="J70" s="14"/>
-      <c r="K70" s="14"/>
-      <c r="L70" s="14"/>
-      <c r="M70" s="14"/>
-      <c r="N70" s="14"/>
-      <c r="O70" s="14"/>
-      <c r="P70" s="19"/>
+      <c r="I70" s="12"/>
+      <c r="J70" s="12"/>
+      <c r="K70" s="12"/>
+      <c r="L70" s="12"/>
+      <c r="M70" s="12"/>
+      <c r="N70" s="12"/>
+      <c r="O70" s="12"/>
+      <c r="P70" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="71" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A71" s="10">
+      <c r="A71" s="8">
         <v>70</v>
       </c>
-      <c r="B71" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C71" s="10" t="s">
+      <c r="B71" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C71" s="8" t="s">
         <v>134</v>
       </c>
-      <c r="D71" s="10" t="s">
+      <c r="D71" s="8" t="s">
         <v>147</v>
       </c>
-      <c r="E71" s="10" t="s">
+      <c r="E71" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="F71" s="11">
+      <c r="F71" s="9">
         <v>700000</v>
       </c>
-      <c r="G71" s="11">
-        <v>0</v>
-      </c>
-      <c r="H71" s="11">
+      <c r="G71" s="9">
+        <v>0</v>
+      </c>
+      <c r="H71" s="9">
         <v>519409196</v>
       </c>
-      <c r="I71" s="14"/>
-      <c r="J71" s="14"/>
-      <c r="K71" s="14"/>
-      <c r="L71" s="14"/>
-      <c r="M71" s="14"/>
-      <c r="N71" s="14"/>
-      <c r="O71" s="14"/>
-      <c r="P71" s="19"/>
+      <c r="I71" s="12"/>
+      <c r="J71" s="12"/>
+      <c r="K71" s="12"/>
+      <c r="L71" s="12"/>
+      <c r="M71" s="12"/>
+      <c r="N71" s="12"/>
+      <c r="O71" s="12"/>
+      <c r="P71" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="72" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A72" s="10">
+      <c r="A72" s="8">
         <v>71</v>
       </c>
-      <c r="B72" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C72" s="10" t="s">
+      <c r="B72" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C72" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D72" s="10" t="s">
+      <c r="D72" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="E72" s="10" t="s">
+      <c r="E72" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="F72" s="11">
+      <c r="F72" s="9">
         <v>1170000</v>
       </c>
-      <c r="G72" s="11">
-        <v>0</v>
-      </c>
-      <c r="H72" s="11">
+      <c r="G72" s="9">
+        <v>0</v>
+      </c>
+      <c r="H72" s="9">
         <v>518239196</v>
       </c>
-      <c r="I72" s="14"/>
-      <c r="J72" s="14"/>
-      <c r="K72" s="14"/>
-      <c r="L72" s="14"/>
-      <c r="M72" s="14"/>
-      <c r="N72" s="14"/>
-      <c r="O72" s="14"/>
-      <c r="P72" s="19"/>
+      <c r="I72" s="12"/>
+      <c r="J72" s="12"/>
+      <c r="K72" s="12"/>
+      <c r="L72" s="12"/>
+      <c r="M72" s="12"/>
+      <c r="N72" s="12"/>
+      <c r="O72" s="12"/>
+      <c r="P72" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="73" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A73" s="10">
+      <c r="A73" s="8">
         <v>72</v>
       </c>
-      <c r="B73" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C73" s="10" t="s">
+      <c r="B73" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C73" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D73" s="10" t="s">
+      <c r="D73" s="8" t="s">
         <v>152</v>
       </c>
-      <c r="E73" s="10" t="s">
+      <c r="E73" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="F73" s="11">
+      <c r="F73" s="9">
         <v>2520000</v>
       </c>
-      <c r="G73" s="11">
-        <v>0</v>
-      </c>
-      <c r="H73" s="11">
+      <c r="G73" s="9">
+        <v>0</v>
+      </c>
+      <c r="H73" s="9">
         <v>515719196</v>
       </c>
-      <c r="I73" s="14"/>
-      <c r="J73" s="14"/>
-      <c r="K73" s="14"/>
-      <c r="L73" s="14"/>
-      <c r="M73" s="14"/>
-      <c r="N73" s="14"/>
-      <c r="O73" s="14"/>
-      <c r="P73" s="19"/>
+      <c r="I73" s="12"/>
+      <c r="J73" s="12"/>
+      <c r="K73" s="12"/>
+      <c r="L73" s="12"/>
+      <c r="M73" s="12"/>
+      <c r="N73" s="12"/>
+      <c r="O73" s="12"/>
+      <c r="P73" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="74" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A74" s="10">
+      <c r="A74" s="8">
         <v>73</v>
       </c>
-      <c r="B74" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C74" s="10" t="s">
+      <c r="B74" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C74" s="8" t="s">
         <v>149</v>
       </c>
-      <c r="D74" s="10" t="s">
+      <c r="D74" s="8" t="s">
         <v>154</v>
       </c>
-      <c r="E74" s="10" t="s">
+      <c r="E74" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F74" s="11">
+      <c r="F74" s="9">
         <v>1730000</v>
       </c>
-      <c r="G74" s="11">
-        <v>0</v>
-      </c>
-      <c r="H74" s="11">
+      <c r="G74" s="9">
+        <v>0</v>
+      </c>
+      <c r="H74" s="9">
         <v>513989196</v>
       </c>
-      <c r="I74" s="14"/>
-      <c r="J74" s="14"/>
-      <c r="K74" s="14"/>
-      <c r="L74" s="14"/>
-      <c r="M74" s="14"/>
-      <c r="N74" s="14"/>
-      <c r="O74" s="14"/>
-      <c r="P74" s="19"/>
+      <c r="I74" s="12"/>
+      <c r="J74" s="12"/>
+      <c r="K74" s="12"/>
+      <c r="L74" s="12"/>
+      <c r="M74" s="12"/>
+      <c r="N74" s="12"/>
+      <c r="O74" s="12"/>
+      <c r="P74" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="75" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A75" s="10">
+      <c r="A75" s="8">
         <v>74</v>
       </c>
-      <c r="B75" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C75" s="10" t="s">
+      <c r="B75" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C75" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D75" s="10" t="s">
+      <c r="D75" s="8" t="s">
         <v>157</v>
       </c>
-      <c r="E75" s="10" t="s">
+      <c r="E75" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F75" s="11">
+      <c r="F75" s="9">
         <v>1760000</v>
       </c>
-      <c r="G75" s="11">
-        <v>0</v>
-      </c>
-      <c r="H75" s="11">
+      <c r="G75" s="9">
+        <v>0</v>
+      </c>
+      <c r="H75" s="9">
         <v>512229196</v>
       </c>
-      <c r="I75" s="14"/>
-      <c r="J75" s="14"/>
-      <c r="K75" s="14"/>
-      <c r="L75" s="14"/>
-      <c r="M75" s="14"/>
-      <c r="N75" s="14"/>
-      <c r="O75" s="14"/>
-      <c r="P75" s="19"/>
+      <c r="I75" s="12"/>
+      <c r="J75" s="12"/>
+      <c r="K75" s="12"/>
+      <c r="L75" s="12"/>
+      <c r="M75" s="12"/>
+      <c r="N75" s="12"/>
+      <c r="O75" s="12"/>
+      <c r="P75" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="76" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A76" s="10">
+      <c r="A76" s="8">
         <v>75</v>
       </c>
-      <c r="B76" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C76" s="10" t="s">
+      <c r="B76" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C76" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D76" s="10" t="s">
+      <c r="D76" s="8" t="s">
         <v>159</v>
       </c>
-      <c r="E76" s="10" t="s">
+      <c r="E76" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="F76" s="11">
+      <c r="F76" s="9">
         <v>2000000</v>
       </c>
-      <c r="G76" s="11">
-        <v>0</v>
-      </c>
-      <c r="H76" s="11">
+      <c r="G76" s="9">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
         <v>510229196</v>
       </c>
-      <c r="I76" s="14"/>
-      <c r="J76" s="14"/>
-      <c r="K76" s="14"/>
-      <c r="L76" s="14"/>
-      <c r="M76" s="14"/>
-      <c r="N76" s="14"/>
-      <c r="O76" s="14"/>
-      <c r="P76" s="19"/>
+      <c r="I76" s="12"/>
+      <c r="J76" s="12"/>
+      <c r="K76" s="12"/>
+      <c r="L76" s="12"/>
+      <c r="M76" s="12"/>
+      <c r="N76" s="12"/>
+      <c r="O76" s="12"/>
+      <c r="P76" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="77" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A77" s="10">
+      <c r="A77" s="8">
         <v>76</v>
       </c>
-      <c r="B77" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C77" s="10" t="s">
+      <c r="B77" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C77" s="8" t="s">
         <v>156</v>
       </c>
-      <c r="D77" s="10" t="s">
+      <c r="D77" s="8" t="s">
         <v>161</v>
       </c>
-      <c r="E77" s="10" t="s">
+      <c r="E77" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="F77" s="11">
+      <c r="F77" s="9">
         <v>1450000</v>
       </c>
-      <c r="G77" s="11">
-        <v>0</v>
-      </c>
-      <c r="H77" s="11">
+      <c r="G77" s="9">
+        <v>0</v>
+      </c>
+      <c r="H77" s="9">
         <v>508779196</v>
       </c>
-      <c r="I77" s="14"/>
-      <c r="J77" s="14"/>
-      <c r="K77" s="14"/>
-      <c r="L77" s="14"/>
-      <c r="M77" s="14"/>
-      <c r="N77" s="14"/>
-      <c r="O77" s="14"/>
-      <c r="P77" s="19"/>
+      <c r="I77" s="12"/>
+      <c r="J77" s="12"/>
+      <c r="K77" s="12"/>
+      <c r="L77" s="12"/>
+      <c r="M77" s="12"/>
+      <c r="N77" s="12"/>
+      <c r="O77" s="12"/>
+      <c r="P77" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="78" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A78" s="10">
+      <c r="A78" s="8">
         <v>77</v>
       </c>
-      <c r="B78" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C78" s="10" t="s">
+      <c r="B78" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C78" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D78" s="10" t="s">
+      <c r="D78" s="8" t="s">
         <v>164</v>
       </c>
-      <c r="E78" s="10" t="s">
+      <c r="E78" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="F78" s="11">
+      <c r="F78" s="9">
         <v>1030000</v>
       </c>
-      <c r="G78" s="11">
-        <v>0</v>
-      </c>
-      <c r="H78" s="11">
+      <c r="G78" s="9">
+        <v>0</v>
+      </c>
+      <c r="H78" s="9">
         <v>507749196</v>
       </c>
-      <c r="I78" s="14"/>
-      <c r="J78" s="14"/>
-      <c r="K78" s="14"/>
-      <c r="L78" s="14"/>
-      <c r="M78" s="14"/>
-      <c r="N78" s="14"/>
-      <c r="O78" s="14"/>
-      <c r="P78" s="19"/>
+      <c r="I78" s="12"/>
+      <c r="J78" s="12"/>
+      <c r="K78" s="12"/>
+      <c r="L78" s="12"/>
+      <c r="M78" s="12"/>
+      <c r="N78" s="12"/>
+      <c r="O78" s="12"/>
+      <c r="P78" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="79" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A79" s="10">
+      <c r="A79" s="8">
         <v>78</v>
       </c>
-      <c r="B79" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C79" s="10" t="s">
+      <c r="B79" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C79" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D79" s="10" t="s">
+      <c r="D79" s="8" t="s">
         <v>166</v>
       </c>
-      <c r="E79" s="10" t="s">
+      <c r="E79" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="F79" s="11">
+      <c r="F79" s="9">
         <v>1060000</v>
       </c>
-      <c r="G79" s="11">
-        <v>0</v>
-      </c>
-      <c r="H79" s="11">
+      <c r="G79" s="9">
+        <v>0</v>
+      </c>
+      <c r="H79" s="9">
         <v>506689196</v>
       </c>
-      <c r="I79" s="14"/>
-      <c r="J79" s="14"/>
-      <c r="K79" s="14"/>
-      <c r="L79" s="14"/>
-      <c r="M79" s="14"/>
-      <c r="N79" s="14"/>
-      <c r="O79" s="14"/>
-      <c r="P79" s="19"/>
+      <c r="I79" s="12"/>
+      <c r="J79" s="12"/>
+      <c r="K79" s="12"/>
+      <c r="L79" s="12"/>
+      <c r="M79" s="12"/>
+      <c r="N79" s="12"/>
+      <c r="O79" s="12"/>
+      <c r="P79" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="80" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A80" s="10">
+      <c r="A80" s="8">
         <v>79</v>
       </c>
-      <c r="B80" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C80" s="10" t="s">
+      <c r="B80" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C80" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D80" s="10" t="s">
+      <c r="D80" s="8" t="s">
         <v>168</v>
       </c>
-      <c r="E80" s="10" t="s">
+      <c r="E80" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="F80" s="11">
+      <c r="F80" s="9">
         <v>350000</v>
       </c>
-      <c r="G80" s="11">
-        <v>0</v>
-      </c>
-      <c r="H80" s="11">
+      <c r="G80" s="9">
+        <v>0</v>
+      </c>
+      <c r="H80" s="9">
         <v>506339196</v>
       </c>
-      <c r="I80" s="14"/>
-      <c r="J80" s="14"/>
-      <c r="K80" s="14"/>
-      <c r="L80" s="14"/>
-      <c r="M80" s="14"/>
-      <c r="N80" s="14"/>
-      <c r="O80" s="14"/>
-      <c r="P80" s="19"/>
+      <c r="I80" s="12"/>
+      <c r="J80" s="12"/>
+      <c r="K80" s="12"/>
+      <c r="L80" s="12"/>
+      <c r="M80" s="12"/>
+      <c r="N80" s="12"/>
+      <c r="O80" s="12"/>
+      <c r="P80" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="81" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A81" s="10">
+      <c r="A81" s="8">
         <v>80</v>
       </c>
-      <c r="B81" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C81" s="10" t="s">
+      <c r="B81" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C81" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D81" s="10" t="s">
+      <c r="D81" s="8" t="s">
         <v>170</v>
       </c>
-      <c r="E81" s="10" t="s">
+      <c r="E81" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F81" s="11">
+      <c r="F81" s="9">
         <v>1300000</v>
       </c>
-      <c r="G81" s="11">
-        <v>0</v>
-      </c>
-      <c r="H81" s="11">
+      <c r="G81" s="9">
+        <v>0</v>
+      </c>
+      <c r="H81" s="9">
         <v>505039196</v>
       </c>
-      <c r="I81" s="14"/>
-      <c r="J81" s="14"/>
-      <c r="K81" s="14"/>
-      <c r="L81" s="14"/>
-      <c r="M81" s="14"/>
-      <c r="N81" s="14"/>
-      <c r="O81" s="14"/>
-      <c r="P81" s="19"/>
+      <c r="I81" s="12"/>
+      <c r="J81" s="12"/>
+      <c r="K81" s="12"/>
+      <c r="L81" s="12"/>
+      <c r="M81" s="12"/>
+      <c r="N81" s="12"/>
+      <c r="O81" s="12"/>
+      <c r="P81" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="82" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A82" s="10">
+      <c r="A82" s="8">
         <v>81</v>
       </c>
-      <c r="B82" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C82" s="10" t="s">
+      <c r="B82" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C82" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D82" s="10" t="s">
+      <c r="D82" s="8" t="s">
         <v>172</v>
       </c>
-      <c r="E82" s="10" t="s">
+      <c r="E82" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="F82" s="11">
+      <c r="F82" s="9">
         <v>240000</v>
       </c>
-      <c r="G82" s="11">
-        <v>0</v>
-      </c>
-      <c r="H82" s="11">
+      <c r="G82" s="9">
+        <v>0</v>
+      </c>
+      <c r="H82" s="9">
         <v>504799196</v>
       </c>
-      <c r="I82" s="14"/>
-      <c r="J82" s="14"/>
-      <c r="K82" s="14"/>
-      <c r="L82" s="14"/>
-      <c r="M82" s="14"/>
-      <c r="N82" s="14"/>
-      <c r="O82" s="14"/>
-      <c r="P82" s="19"/>
+      <c r="I82" s="12"/>
+      <c r="J82" s="12"/>
+      <c r="K82" s="12"/>
+      <c r="L82" s="12"/>
+      <c r="M82" s="12"/>
+      <c r="N82" s="12"/>
+      <c r="O82" s="12"/>
+      <c r="P82" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="83" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A83" s="10">
+      <c r="A83" s="8">
         <v>82</v>
       </c>
-      <c r="B83" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C83" s="10" t="s">
+      <c r="B83" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C83" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D83" s="10" t="s">
+      <c r="D83" s="8" t="s">
         <v>174</v>
       </c>
-      <c r="E83" s="10" t="s">
+      <c r="E83" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="F83" s="11">
+      <c r="F83" s="9">
         <v>2540000</v>
       </c>
-      <c r="G83" s="11">
-        <v>0</v>
-      </c>
-      <c r="H83" s="11">
+      <c r="G83" s="9">
+        <v>0</v>
+      </c>
+      <c r="H83" s="9">
         <v>502259196</v>
       </c>
-      <c r="I83" s="14"/>
-      <c r="J83" s="14"/>
-      <c r="K83" s="14"/>
-      <c r="L83" s="14"/>
-      <c r="M83" s="14"/>
-      <c r="N83" s="14"/>
-      <c r="O83" s="14"/>
-      <c r="P83" s="19"/>
+      <c r="I83" s="12"/>
+      <c r="J83" s="12"/>
+      <c r="K83" s="12"/>
+      <c r="L83" s="12"/>
+      <c r="M83" s="12"/>
+      <c r="N83" s="12"/>
+      <c r="O83" s="12"/>
+      <c r="P83" s="17" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="84" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A84" s="10">
+      <c r="A84" s="8">
         <v>83</v>
       </c>
-      <c r="B84" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C84" s="10" t="s">
+      <c r="B84" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C84" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D84" s="10" t="s">
+      <c r="D84" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="E84" s="10" t="s">
+      <c r="E84" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F84" s="11">
+      <c r="F84" s="9">
         <v>25000</v>
       </c>
-      <c r="G84" s="11">
-        <v>0</v>
-      </c>
-      <c r="H84" s="11">
+      <c r="G84" s="9">
+        <v>0</v>
+      </c>
+      <c r="H84" s="9">
         <v>502234196</v>
       </c>
-      <c r="I84" s="14"/>
-      <c r="J84" s="14"/>
-      <c r="K84" s="14"/>
-      <c r="L84" s="14"/>
-      <c r="M84" s="18"/>
-      <c r="N84" s="18"/>
-      <c r="O84" s="18">
+      <c r="I84" s="12"/>
+      <c r="J84" s="12"/>
+      <c r="K84" s="12"/>
+      <c r="L84" s="12"/>
+      <c r="M84" s="16"/>
+      <c r="N84" s="16"/>
+      <c r="O84" s="16">
         <v>25000</v>
       </c>
-      <c r="P84" s="14"/>
+      <c r="P84" s="12"/>
     </row>
     <row r="85" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A85" s="10">
+      <c r="A85" s="8">
         <v>84</v>
       </c>
-      <c r="B85" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="C85" s="10" t="s">
+      <c r="B85" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C85" s="8" t="s">
         <v>163</v>
       </c>
-      <c r="D85" s="10" t="s">
+      <c r="D85" s="8" t="s">
         <v>176</v>
       </c>
-      <c r="E85" s="10" t="s">
+      <c r="E85" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="F85" s="11">
+      <c r="F85" s="9">
         <v>50000000</v>
       </c>
-      <c r="G85" s="11">
-        <v>0</v>
-      </c>
-      <c r="H85" s="11">
+      <c r="G85" s="9">
+        <v>0</v>
+      </c>
+      <c r="H85" s="9">
         <v>452234196</v>
       </c>
-      <c r="I85" s="14"/>
-      <c r="J85" s="14"/>
-      <c r="K85" s="14"/>
-      <c r="L85" s="14"/>
-      <c r="M85" s="14"/>
-      <c r="N85" s="14"/>
-      <c r="O85" s="14"/>
-      <c r="P85" s="14" t="s">
+      <c r="I85" s="12"/>
+      <c r="J85" s="12"/>
+      <c r="K85" s="12"/>
+      <c r="L85" s="12"/>
+      <c r="M85" s="12"/>
+      <c r="N85" s="12"/>
+      <c r="O85" s="12"/>
+      <c r="P85" s="12" t="s">
         <v>187</v>
       </c>
     </row>

--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/شهریور کامل.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/شهریور کامل.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\رسالت ابوالفضل\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F42EB158-6E59-46A6-8B9F-CFB57F53C30E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E1FCA7-DF73-4DDC-9765-56FD333BA26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="846" uniqueCount="209">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="210">
   <si>
     <t>صورت حساب سپرده</t>
   </si>
@@ -661,6 +661,9 @@
   </si>
   <si>
     <t>حمل بار نمایشگاه</t>
+  </si>
+  <si>
+    <t>انتقالی از مهر قدیم حساب به حساب</t>
   </si>
 </sst>
 </file>
@@ -704,7 +707,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -765,12 +768,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -799,7 +796,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -854,12 +851,6 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -878,10 +869,13 @@
     <xf numFmtId="3" fontId="4" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1214,30 +1208,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
+      <c r="A1" s="24" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
     </row>
     <row r="2" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
     </row>
     <row r="3" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
@@ -3705,17 +3699,17 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="19" t="s">
+      <c r="A88" s="25" t="s">
         <v>178</v>
       </c>
-      <c r="B88" s="19"/>
-      <c r="C88" s="19"/>
-      <c r="D88" s="19"/>
-      <c r="E88" s="19"/>
-      <c r="F88" s="19"/>
-      <c r="G88" s="19"/>
-      <c r="H88" s="19"/>
-      <c r="I88" s="19"/>
+      <c r="B88" s="25"/>
+      <c r="C88" s="25"/>
+      <c r="D88" s="25"/>
+      <c r="E88" s="25"/>
+      <c r="F88" s="25"/>
+      <c r="G88" s="25"/>
+      <c r="H88" s="25"/>
+      <c r="I88" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3875,7 +3869,7 @@
       <c r="E4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="9">
+      <c r="F4" s="23">
         <v>59000</v>
       </c>
       <c r="G4" s="9">
@@ -3915,7 +3909,7 @@
       <c r="E5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="9">
+      <c r="F5" s="23">
         <v>3300000</v>
       </c>
       <c r="G5" s="9">
@@ -3958,7 +3952,7 @@
       <c r="F6" s="9">
         <v>0</v>
       </c>
-      <c r="G6" s="25">
+      <c r="G6" s="23">
         <v>49570000</v>
       </c>
       <c r="H6" s="9">
@@ -3973,7 +3967,7 @@
       <c r="M6" s="12"/>
       <c r="N6" s="12"/>
       <c r="O6" s="12"/>
-      <c r="P6" s="26"/>
+      <c r="P6" s="12"/>
     </row>
     <row r="7" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A7" s="8">
@@ -3991,7 +3985,7 @@
       <c r="E7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="9">
+      <c r="F7" s="23">
         <v>2381000</v>
       </c>
       <c r="G7" s="9">
@@ -4067,7 +4061,7 @@
       <c r="E9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="9">
+      <c r="F9" s="23">
         <v>2500000</v>
       </c>
       <c r="G9" s="9">
@@ -4107,7 +4101,7 @@
       <c r="E10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="9">
+      <c r="F10" s="23">
         <v>9600000</v>
       </c>
       <c r="G10" s="9">
@@ -4183,7 +4177,7 @@
       <c r="E12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="9">
+      <c r="F12" s="23">
         <v>35000000</v>
       </c>
       <c r="G12" s="9">
@@ -4223,7 +4217,7 @@
       <c r="E13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="9">
+      <c r="F13" s="23">
         <v>2250000</v>
       </c>
       <c r="G13" s="9">
@@ -4263,7 +4257,7 @@
       <c r="E14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="9">
+      <c r="F14" s="23">
         <v>2756000</v>
       </c>
       <c r="G14" s="9">
@@ -4306,7 +4300,7 @@
       <c r="F15" s="9">
         <v>0</v>
       </c>
-      <c r="G15" s="25">
+      <c r="G15" s="23">
         <v>60000000</v>
       </c>
       <c r="H15" s="9">
@@ -4321,7 +4315,7 @@
       <c r="M15" s="12"/>
       <c r="N15" s="12"/>
       <c r="O15" s="12"/>
-      <c r="P15" s="26"/>
+      <c r="P15" s="12"/>
     </row>
     <row r="16" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="8">
@@ -4342,7 +4336,7 @@
       <c r="F16" s="9">
         <v>0</v>
       </c>
-      <c r="G16" s="25">
+      <c r="G16" s="23">
         <v>150000000</v>
       </c>
       <c r="H16" s="9">
@@ -4357,7 +4351,7 @@
       <c r="M16" s="12"/>
       <c r="N16" s="12"/>
       <c r="O16" s="12"/>
-      <c r="P16" s="26"/>
+      <c r="P16" s="12"/>
     </row>
     <row r="17" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="8">
@@ -4378,7 +4372,7 @@
       <c r="F17" s="9">
         <v>0</v>
       </c>
-      <c r="G17" s="25">
+      <c r="G17" s="23">
         <v>15300000</v>
       </c>
       <c r="H17" s="9">
@@ -4393,7 +4387,7 @@
       <c r="M17" s="12"/>
       <c r="N17" s="12"/>
       <c r="O17" s="12"/>
-      <c r="P17" s="26"/>
+      <c r="P17" s="12"/>
     </row>
     <row r="18" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A18" s="8">
@@ -4429,7 +4423,7 @@
       <c r="O18" s="16">
         <v>53800</v>
       </c>
-      <c r="P18" s="26"/>
+      <c r="P18" s="12"/>
     </row>
     <row r="19" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="8">
@@ -4447,7 +4441,7 @@
       <c r="E19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="9">
+      <c r="F19" s="23">
         <v>150000000</v>
       </c>
       <c r="G19" s="9">
@@ -4523,7 +4517,7 @@
       <c r="E21" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F21" s="9">
+      <c r="F21" s="23">
         <v>1300000</v>
       </c>
       <c r="G21" s="9">
@@ -4599,7 +4593,7 @@
       <c r="E23" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="9">
+      <c r="F23" s="23">
         <v>3000000</v>
       </c>
       <c r="G23" s="9">
@@ -4639,7 +4633,7 @@
       <c r="E24" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="9">
+      <c r="F24" s="23">
         <v>1630000</v>
       </c>
       <c r="G24" s="9">
@@ -4664,74 +4658,74 @@
       </c>
     </row>
     <row r="25" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="22">
+      <c r="A25" s="20">
         <v>24</v>
       </c>
-      <c r="B25" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="22" t="s">
+      <c r="B25" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="22" t="s">
+      <c r="D25" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="22" t="s">
+      <c r="E25" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="21">
         <v>14400000</v>
       </c>
-      <c r="G25" s="23">
-        <v>0</v>
-      </c>
-      <c r="H25" s="23">
+      <c r="G25" s="21">
+        <v>0</v>
+      </c>
+      <c r="H25" s="21">
         <v>54918696</v>
       </c>
-      <c r="I25" s="24"/>
-      <c r="J25" s="24"/>
-      <c r="K25" s="24"/>
-      <c r="L25" s="24"/>
-      <c r="M25" s="24"/>
-      <c r="N25" s="24"/>
-      <c r="O25" s="24"/>
-      <c r="P25" s="24" t="s">
+      <c r="I25" s="22"/>
+      <c r="J25" s="22"/>
+      <c r="K25" s="22"/>
+      <c r="L25" s="22"/>
+      <c r="M25" s="22"/>
+      <c r="N25" s="22"/>
+      <c r="O25" s="22"/>
+      <c r="P25" s="22" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="22">
+      <c r="A26" s="20">
         <v>25</v>
       </c>
-      <c r="B26" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="22" t="s">
+      <c r="B26" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="22" t="s">
+      <c r="D26" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="22" t="s">
+      <c r="E26" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="21">
         <v>33600000</v>
       </c>
-      <c r="G26" s="23">
-        <v>0</v>
-      </c>
-      <c r="H26" s="23">
+      <c r="G26" s="21">
+        <v>0</v>
+      </c>
+      <c r="H26" s="21">
         <v>21318696</v>
       </c>
-      <c r="I26" s="24"/>
-      <c r="J26" s="24"/>
-      <c r="K26" s="24"/>
-      <c r="L26" s="24"/>
-      <c r="M26" s="24"/>
-      <c r="N26" s="24"/>
-      <c r="O26" s="24"/>
-      <c r="P26" s="24" t="s">
+      <c r="I26" s="22"/>
+      <c r="J26" s="22"/>
+      <c r="K26" s="22"/>
+      <c r="L26" s="22"/>
+      <c r="M26" s="22"/>
+      <c r="N26" s="22"/>
+      <c r="O26" s="22"/>
+      <c r="P26" s="22" t="s">
         <v>192</v>
       </c>
     </row>
@@ -4754,7 +4748,7 @@
       <c r="F27" s="9">
         <v>0</v>
       </c>
-      <c r="G27" s="21">
+      <c r="G27" s="23">
         <v>773900000</v>
       </c>
       <c r="H27" s="9">
@@ -4762,12 +4756,16 @@
       </c>
       <c r="I27" s="12"/>
       <c r="J27" s="12"/>
-      <c r="K27" s="20"/>
+      <c r="K27" s="16">
+        <v>326</v>
+      </c>
       <c r="L27" s="12"/>
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
-      <c r="P27" s="20"/>
+      <c r="P27" s="26" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="28" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A28" s="8">
@@ -4821,7 +4819,7 @@
       <c r="E29" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="23">
         <v>50000000</v>
       </c>
       <c r="G29" s="9">
@@ -4933,7 +4931,7 @@
       <c r="E32" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="23">
         <v>2000000</v>
       </c>
       <c r="G32" s="9">
@@ -4947,7 +4945,9 @@
       </c>
       <c r="J32" s="12"/>
       <c r="K32" s="12"/>
-      <c r="L32" s="27"/>
+      <c r="L32" s="16">
+        <v>394</v>
+      </c>
       <c r="M32" s="12"/>
       <c r="N32" s="12"/>
       <c r="O32" s="12"/>
@@ -4978,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="H33" s="9">
-        <v>698482696</v>
+        <v>720082696</v>
       </c>
       <c r="I33" s="16"/>
       <c r="J33" s="12"/>
@@ -5079,7 +5079,7 @@
       <c r="E36" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="23">
         <v>18000000</v>
       </c>
       <c r="G36" s="9">
@@ -5088,10 +5088,14 @@
       <c r="H36" s="9">
         <v>630068196</v>
       </c>
-      <c r="I36" s="16"/>
+      <c r="I36" s="16">
+        <v>317</v>
+      </c>
       <c r="J36" s="12"/>
       <c r="K36" s="12"/>
-      <c r="L36" s="16"/>
+      <c r="L36" s="16">
+        <v>394</v>
+      </c>
       <c r="M36" s="12"/>
       <c r="N36" s="12"/>
       <c r="O36" s="12"/>
@@ -5100,38 +5104,38 @@
       </c>
     </row>
     <row r="37" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="22">
+      <c r="A37" s="20">
         <v>36</v>
       </c>
-      <c r="B37" s="22" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="22" t="s">
+      <c r="B37" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="22" t="s">
+      <c r="D37" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="22" t="s">
+      <c r="E37" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="F37" s="23">
-        <v>0</v>
-      </c>
-      <c r="G37" s="23">
+      <c r="F37" s="21">
+        <v>0</v>
+      </c>
+      <c r="G37" s="21">
         <v>48000000</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="21">
         <v>678068196</v>
       </c>
-      <c r="I37" s="24"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
-      <c r="N37" s="24"/>
-      <c r="O37" s="24"/>
-      <c r="P37" s="24" t="s">
+      <c r="I37" s="22"/>
+      <c r="J37" s="22"/>
+      <c r="K37" s="22"/>
+      <c r="L37" s="22"/>
+      <c r="M37" s="22"/>
+      <c r="N37" s="22"/>
+      <c r="O37" s="22"/>
+      <c r="P37" s="22" t="s">
         <v>196</v>
       </c>
     </row>
@@ -5370,7 +5374,7 @@
       <c r="F44" s="9">
         <v>0</v>
       </c>
-      <c r="G44" s="21">
+      <c r="G44" s="19">
         <v>104000000</v>
       </c>
       <c r="H44" s="9">
@@ -5378,12 +5382,12 @@
       </c>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
-      <c r="K44" s="20"/>
+      <c r="K44" s="18"/>
       <c r="L44" s="12"/>
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
       <c r="O44" s="12"/>
-      <c r="P44" s="20"/>
+      <c r="P44" s="18"/>
     </row>
     <row r="45" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A45" s="8">

--- a/حسابداری/بانک ها/رسالت ابوالفضل/1405/شهریور کامل.xlsx
+++ b/حسابداری/بانک ها/رسالت ابوالفضل/1405/شهریور کامل.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\حسابداری باکسینو\حسابداری\بانک ها\رسالت ابوالفضل\1405\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E1FCA7-DF73-4DDC-9765-56FD333BA26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91666267-BD6D-4B8E-8F12-F80BB62CAD0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,6 +16,9 @@
     <sheet name="Table1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet1!$A$1:$P$85</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="210">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="848" uniqueCount="211">
   <si>
     <t>صورت حساب سپرده</t>
   </si>
@@ -633,9 +636,6 @@
     <t>بابت خرید باطری، ماژیک و میخ از کارت شخصیم</t>
   </si>
   <si>
-    <t>بلیط اتوبوس اصفهان</t>
-  </si>
-  <si>
     <t>3 کیلو حلوا مسقطی فاخر</t>
   </si>
   <si>
@@ -645,25 +645,31 @@
     <t>کارتن بسته بندی کوچک</t>
   </si>
   <si>
-    <t>اتوبوس شیراز</t>
-  </si>
-  <si>
     <t>کاغذ a4</t>
   </si>
   <si>
     <t>چسب پاک کن</t>
   </si>
   <si>
-    <t>بتنور سفر</t>
-  </si>
-  <si>
     <t>سفر نمایشگاه</t>
   </si>
   <si>
-    <t>حمل بار نمایشگاه</t>
-  </si>
-  <si>
     <t>انتقالی از مهر قدیم حساب به حساب</t>
+  </si>
+  <si>
+    <t>*** حمل بار نمایشگاه ***</t>
+  </si>
+  <si>
+    <t>*** اتوبوس شیراز ***</t>
+  </si>
+  <si>
+    <t>*** بتنور سفر ***</t>
+  </si>
+  <si>
+    <t>*** اسنپ جا مانده ی نمایشگاه ***</t>
+  </si>
+  <si>
+    <t>*** بلیط اتوبوس اصفهان ***</t>
   </si>
 </sst>
 </file>
@@ -680,12 +686,14 @@
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Tahoma"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -707,7 +715,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -765,6 +773,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -854,9 +868,6 @@
     <xf numFmtId="0" fontId="4" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="4" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="4" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -875,7 +886,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="11" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1208,30 +1222,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A1" s="24" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
+      <c r="A1" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
     </row>
     <row r="2" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A2" s="25" t="s">
+      <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
     </row>
     <row r="3" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="3" t="s">
@@ -3699,17 +3713,17 @@
       </c>
     </row>
     <row r="88" spans="1:9" ht="24.95" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A88" s="25" t="s">
+      <c r="A88" s="24" t="s">
         <v>178</v>
       </c>
-      <c r="B88" s="25"/>
-      <c r="C88" s="25"/>
-      <c r="D88" s="25"/>
-      <c r="E88" s="25"/>
-      <c r="F88" s="25"/>
-      <c r="G88" s="25"/>
-      <c r="H88" s="25"/>
-      <c r="I88" s="25"/>
+      <c r="B88" s="24"/>
+      <c r="C88" s="24"/>
+      <c r="D88" s="24"/>
+      <c r="E88" s="24"/>
+      <c r="F88" s="24"/>
+      <c r="G88" s="24"/>
+      <c r="H88" s="24"/>
+      <c r="I88" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -3869,7 +3883,7 @@
       <c r="E4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="23">
+      <c r="F4" s="22">
         <v>59000</v>
       </c>
       <c r="G4" s="9">
@@ -3909,7 +3923,7 @@
       <c r="E5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="23">
+      <c r="F5" s="22">
         <v>3300000</v>
       </c>
       <c r="G5" s="9">
@@ -3952,7 +3966,7 @@
       <c r="F6" s="9">
         <v>0</v>
       </c>
-      <c r="G6" s="23">
+      <c r="G6" s="22">
         <v>49570000</v>
       </c>
       <c r="H6" s="9">
@@ -3985,7 +3999,7 @@
       <c r="E7" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="F7" s="23">
+      <c r="F7" s="22">
         <v>2381000</v>
       </c>
       <c r="G7" s="9">
@@ -4025,7 +4039,7 @@
       <c r="E8" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="9">
+      <c r="F8" s="22">
         <v>9000</v>
       </c>
       <c r="G8" s="9">
@@ -4038,8 +4052,12 @@
       <c r="J8" s="12"/>
       <c r="K8" s="12"/>
       <c r="L8" s="12"/>
-      <c r="M8" s="16"/>
-      <c r="N8" s="16"/>
+      <c r="M8" s="16">
+        <v>390</v>
+      </c>
+      <c r="N8" s="16">
+        <v>448</v>
+      </c>
       <c r="O8" s="16">
         <v>9000</v>
       </c>
@@ -4061,7 +4079,7 @@
       <c r="E9" s="8" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="22">
         <v>2500000</v>
       </c>
       <c r="G9" s="9">
@@ -4101,7 +4119,7 @@
       <c r="E10" s="8" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="23">
+      <c r="F10" s="22">
         <v>9600000</v>
       </c>
       <c r="G10" s="9">
@@ -4141,7 +4159,7 @@
       <c r="E11" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="9">
+      <c r="F11" s="22">
         <v>18600</v>
       </c>
       <c r="G11" s="9">
@@ -4154,8 +4172,12 @@
       <c r="J11" s="12"/>
       <c r="K11" s="12"/>
       <c r="L11" s="12"/>
-      <c r="M11" s="16"/>
-      <c r="N11" s="16"/>
+      <c r="M11" s="16">
+        <v>390</v>
+      </c>
+      <c r="N11" s="16">
+        <v>448</v>
+      </c>
       <c r="O11" s="16">
         <v>18600</v>
       </c>
@@ -4177,7 +4199,7 @@
       <c r="E12" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F12" s="23">
+      <c r="F12" s="22">
         <v>35000000</v>
       </c>
       <c r="G12" s="9">
@@ -4217,7 +4239,7 @@
       <c r="E13" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="22">
         <v>2250000</v>
       </c>
       <c r="G13" s="9">
@@ -4257,7 +4279,7 @@
       <c r="E14" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="22">
         <v>2756000</v>
       </c>
       <c r="G14" s="9">
@@ -4300,7 +4322,7 @@
       <c r="F15" s="9">
         <v>0</v>
       </c>
-      <c r="G15" s="23">
+      <c r="G15" s="22">
         <v>60000000</v>
       </c>
       <c r="H15" s="9">
@@ -4336,7 +4358,7 @@
       <c r="F16" s="9">
         <v>0</v>
       </c>
-      <c r="G16" s="23">
+      <c r="G16" s="22">
         <v>150000000</v>
       </c>
       <c r="H16" s="9">
@@ -4372,7 +4394,7 @@
       <c r="F17" s="9">
         <v>0</v>
       </c>
-      <c r="G17" s="23">
+      <c r="G17" s="22">
         <v>15300000</v>
       </c>
       <c r="H17" s="9">
@@ -4405,7 +4427,7 @@
       <c r="E18" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F18" s="9">
+      <c r="F18" s="22">
         <v>53800</v>
       </c>
       <c r="G18" s="9">
@@ -4418,8 +4440,12 @@
       <c r="J18" s="12"/>
       <c r="K18" s="12"/>
       <c r="L18" s="12"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
+      <c r="M18" s="16">
+        <v>390</v>
+      </c>
+      <c r="N18" s="16">
+        <v>448</v>
+      </c>
       <c r="O18" s="16">
         <v>53800</v>
       </c>
@@ -4441,7 +4467,7 @@
       <c r="E19" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="23">
+      <c r="F19" s="22">
         <v>150000000</v>
       </c>
       <c r="G19" s="9">
@@ -4481,7 +4507,7 @@
       <c r="E20" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F20" s="9">
+      <c r="F20" s="22">
         <v>9000</v>
       </c>
       <c r="G20" s="9">
@@ -4494,8 +4520,12 @@
       <c r="J20" s="12"/>
       <c r="K20" s="12"/>
       <c r="L20" s="12"/>
-      <c r="M20" s="16"/>
-      <c r="N20" s="16"/>
+      <c r="M20" s="16">
+        <v>390</v>
+      </c>
+      <c r="N20" s="16">
+        <v>448</v>
+      </c>
       <c r="O20" s="16">
         <v>9000</v>
       </c>
@@ -4517,7 +4547,7 @@
       <c r="E21" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="22">
         <v>1300000</v>
       </c>
       <c r="G21" s="9">
@@ -4557,7 +4587,7 @@
       <c r="E22" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F22" s="9">
+      <c r="F22" s="22">
         <v>9000</v>
       </c>
       <c r="G22" s="9">
@@ -4570,8 +4600,12 @@
       <c r="J22" s="12"/>
       <c r="K22" s="12"/>
       <c r="L22" s="12"/>
-      <c r="M22" s="16"/>
-      <c r="N22" s="16"/>
+      <c r="M22" s="16">
+        <v>390</v>
+      </c>
+      <c r="N22" s="16">
+        <v>448</v>
+      </c>
       <c r="O22" s="16">
         <v>9000</v>
       </c>
@@ -4593,7 +4627,7 @@
       <c r="E23" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="22">
         <v>3000000</v>
       </c>
       <c r="G23" s="9">
@@ -4633,7 +4667,7 @@
       <c r="E24" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="22">
         <v>1630000</v>
       </c>
       <c r="G24" s="9">
@@ -4658,74 +4692,74 @@
       </c>
     </row>
     <row r="25" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A25" s="20">
+      <c r="A25" s="19">
         <v>24</v>
       </c>
-      <c r="B25" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C25" s="20" t="s">
+      <c r="B25" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="E25" s="20" t="s">
+      <c r="E25" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="F25" s="21">
+      <c r="F25" s="20">
         <v>14400000</v>
       </c>
-      <c r="G25" s="21">
-        <v>0</v>
-      </c>
-      <c r="H25" s="21">
+      <c r="G25" s="20">
+        <v>0</v>
+      </c>
+      <c r="H25" s="20">
         <v>54918696</v>
       </c>
-      <c r="I25" s="22"/>
-      <c r="J25" s="22"/>
-      <c r="K25" s="22"/>
-      <c r="L25" s="22"/>
-      <c r="M25" s="22"/>
-      <c r="N25" s="22"/>
-      <c r="O25" s="22"/>
-      <c r="P25" s="22" t="s">
+      <c r="I25" s="21"/>
+      <c r="J25" s="21"/>
+      <c r="K25" s="21"/>
+      <c r="L25" s="21"/>
+      <c r="M25" s="21"/>
+      <c r="N25" s="21"/>
+      <c r="O25" s="21"/>
+      <c r="P25" s="21" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A26" s="20">
+      <c r="A26" s="19">
         <v>25</v>
       </c>
-      <c r="B26" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C26" s="20" t="s">
+      <c r="B26" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="19" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="19" t="s">
         <v>66</v>
       </c>
-      <c r="F26" s="21">
+      <c r="F26" s="20">
         <v>33600000</v>
       </c>
-      <c r="G26" s="21">
-        <v>0</v>
-      </c>
-      <c r="H26" s="21">
+      <c r="G26" s="20">
+        <v>0</v>
+      </c>
+      <c r="H26" s="20">
         <v>21318696</v>
       </c>
-      <c r="I26" s="22"/>
-      <c r="J26" s="22"/>
-      <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22" t="s">
+      <c r="I26" s="21"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
+      <c r="N26" s="21"/>
+      <c r="O26" s="21"/>
+      <c r="P26" s="21" t="s">
         <v>192</v>
       </c>
     </row>
@@ -4748,7 +4782,7 @@
       <c r="F27" s="9">
         <v>0</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="22">
         <v>773900000</v>
       </c>
       <c r="H27" s="9">
@@ -4763,8 +4797,8 @@
       <c r="M27" s="12"/>
       <c r="N27" s="12"/>
       <c r="O27" s="12"/>
-      <c r="P27" s="26" t="s">
-        <v>209</v>
+      <c r="P27" s="12" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4783,7 +4817,7 @@
       <c r="E28" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="22">
         <v>25000</v>
       </c>
       <c r="G28" s="9">
@@ -4796,8 +4830,12 @@
       <c r="J28" s="12"/>
       <c r="K28" s="12"/>
       <c r="L28" s="12"/>
-      <c r="M28" s="16"/>
-      <c r="N28" s="16"/>
+      <c r="M28" s="16">
+        <v>390</v>
+      </c>
+      <c r="N28" s="16">
+        <v>448</v>
+      </c>
       <c r="O28" s="16">
         <v>25000</v>
       </c>
@@ -4819,7 +4857,7 @@
       <c r="E29" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="22">
         <v>50000000</v>
       </c>
       <c r="G29" s="9">
@@ -4859,7 +4897,7 @@
       <c r="E30" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="22">
         <v>23100000</v>
       </c>
       <c r="G30" s="9">
@@ -4868,15 +4906,19 @@
       <c r="H30" s="9">
         <v>722093696</v>
       </c>
-      <c r="I30" s="12"/>
+      <c r="I30" s="16">
+        <v>381</v>
+      </c>
       <c r="J30" s="12"/>
       <c r="K30" s="12"/>
-      <c r="L30" s="12"/>
+      <c r="L30" s="16">
+        <v>439</v>
+      </c>
       <c r="M30" s="12"/>
       <c r="N30" s="12"/>
       <c r="O30" s="12"/>
       <c r="P30" s="17" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -4895,7 +4937,7 @@
       <c r="E31" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="22">
         <v>11000</v>
       </c>
       <c r="G31" s="9">
@@ -4908,8 +4950,12 @@
       <c r="J31" s="12"/>
       <c r="K31" s="12"/>
       <c r="L31" s="12"/>
-      <c r="M31" s="16"/>
-      <c r="N31" s="16"/>
+      <c r="M31" s="16">
+        <v>390</v>
+      </c>
+      <c r="N31" s="16">
+        <v>448</v>
+      </c>
       <c r="O31" s="16">
         <v>11000</v>
       </c>
@@ -4931,7 +4977,7 @@
       <c r="E32" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="F32" s="23">
+      <c r="F32" s="22">
         <v>2000000</v>
       </c>
       <c r="G32" s="9">
@@ -4971,7 +5017,7 @@
       <c r="E33" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="22">
         <v>21600000</v>
       </c>
       <c r="G33" s="9">
@@ -4980,15 +5026,19 @@
       <c r="H33" s="9">
         <v>720082696</v>
       </c>
-      <c r="I33" s="16"/>
+      <c r="I33" s="16">
+        <v>382</v>
+      </c>
       <c r="J33" s="12"/>
       <c r="K33" s="12"/>
-      <c r="L33" s="16"/>
+      <c r="L33" s="16">
+        <v>440</v>
+      </c>
       <c r="M33" s="12"/>
       <c r="N33" s="12"/>
       <c r="O33" s="12"/>
       <c r="P33" s="12" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="34" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5007,7 +5057,7 @@
       <c r="E34" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="22">
         <v>50400000</v>
       </c>
       <c r="G34" s="9">
@@ -5016,15 +5066,19 @@
       <c r="H34" s="9">
         <v>648082696</v>
       </c>
-      <c r="I34" s="12"/>
+      <c r="I34" s="16">
+        <v>383</v>
+      </c>
       <c r="J34" s="12"/>
       <c r="K34" s="12"/>
-      <c r="L34" s="12"/>
+      <c r="L34" s="16">
+        <v>441</v>
+      </c>
       <c r="M34" s="12"/>
       <c r="N34" s="12"/>
       <c r="O34" s="12"/>
       <c r="P34" s="17" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="35" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5043,7 +5097,7 @@
       <c r="E35" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="22">
         <v>14500</v>
       </c>
       <c r="G35" s="9">
@@ -5056,8 +5110,12 @@
       <c r="J35" s="12"/>
       <c r="K35" s="12"/>
       <c r="L35" s="12"/>
-      <c r="M35" s="16"/>
-      <c r="N35" s="16"/>
+      <c r="M35" s="16">
+        <v>390</v>
+      </c>
+      <c r="N35" s="16">
+        <v>448</v>
+      </c>
       <c r="O35" s="16">
         <v>14500</v>
       </c>
@@ -5079,7 +5137,7 @@
       <c r="E36" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="22">
         <v>18000000</v>
       </c>
       <c r="G36" s="9">
@@ -5104,38 +5162,38 @@
       </c>
     </row>
     <row r="37" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="20">
+      <c r="A37" s="19">
         <v>36</v>
       </c>
-      <c r="B37" s="20" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="20" t="s">
+      <c r="B37" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="19" t="s">
         <v>83</v>
       </c>
-      <c r="D37" s="20" t="s">
+      <c r="D37" s="19" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="20" t="s">
+      <c r="E37" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="F37" s="21">
-        <v>0</v>
-      </c>
-      <c r="G37" s="21">
+      <c r="F37" s="20">
+        <v>0</v>
+      </c>
+      <c r="G37" s="20">
         <v>48000000</v>
       </c>
-      <c r="H37" s="21">
+      <c r="H37" s="20">
         <v>678068196</v>
       </c>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="22" t="s">
+      <c r="I37" s="21"/>
+      <c r="J37" s="21"/>
+      <c r="K37" s="21"/>
+      <c r="L37" s="21"/>
+      <c r="M37" s="21"/>
+      <c r="N37" s="21"/>
+      <c r="O37" s="21"/>
+      <c r="P37" s="21" t="s">
         <v>196</v>
       </c>
     </row>
@@ -5155,7 +5213,7 @@
       <c r="E38" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="22">
         <v>11400000</v>
       </c>
       <c r="G38" s="9">
@@ -5164,15 +5222,19 @@
       <c r="H38" s="9">
         <v>666668196</v>
       </c>
-      <c r="I38" s="16"/>
+      <c r="I38" s="16">
+        <v>378</v>
+      </c>
       <c r="J38" s="12"/>
       <c r="K38" s="12"/>
-      <c r="L38" s="16"/>
+      <c r="L38" s="16">
+        <v>436</v>
+      </c>
       <c r="M38" s="12"/>
       <c r="N38" s="12"/>
       <c r="O38" s="12"/>
       <c r="P38" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="39" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5191,7 +5253,7 @@
       <c r="E39" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="22">
         <v>11000</v>
       </c>
       <c r="G39" s="9">
@@ -5204,8 +5266,12 @@
       <c r="J39" s="12"/>
       <c r="K39" s="12"/>
       <c r="L39" s="12"/>
-      <c r="M39" s="16"/>
-      <c r="N39" s="16"/>
+      <c r="M39" s="16">
+        <v>390</v>
+      </c>
+      <c r="N39" s="16">
+        <v>448</v>
+      </c>
       <c r="O39" s="16">
         <v>11000</v>
       </c>
@@ -5227,7 +5293,7 @@
       <c r="E40" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="22">
         <v>700000</v>
       </c>
       <c r="G40" s="9">
@@ -5236,15 +5302,19 @@
       <c r="H40" s="9">
         <v>665957196</v>
       </c>
-      <c r="I40" s="16"/>
+      <c r="I40" s="16">
+        <v>379</v>
+      </c>
       <c r="J40" s="12"/>
       <c r="K40" s="12"/>
-      <c r="L40" s="16"/>
+      <c r="L40" s="16">
+        <v>437</v>
+      </c>
       <c r="M40" s="12"/>
       <c r="N40" s="12"/>
       <c r="O40" s="12"/>
       <c r="P40" s="12" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="41" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5263,7 +5333,7 @@
       <c r="E41" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="22">
         <v>8900000</v>
       </c>
       <c r="G41" s="9">
@@ -5272,15 +5342,19 @@
       <c r="H41" s="9">
         <v>657057196</v>
       </c>
-      <c r="I41" s="12"/>
+      <c r="I41" s="16">
+        <v>384</v>
+      </c>
       <c r="J41" s="12"/>
       <c r="K41" s="12"/>
-      <c r="L41" s="12"/>
+      <c r="L41" s="16">
+        <v>442</v>
+      </c>
       <c r="M41" s="12"/>
       <c r="N41" s="12"/>
       <c r="O41" s="12"/>
       <c r="P41" s="17" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
     </row>
     <row r="42" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5299,7 +5373,7 @@
       <c r="E42" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="22">
         <v>850000</v>
       </c>
       <c r="G42" s="9">
@@ -5308,15 +5382,19 @@
       <c r="H42" s="9">
         <v>656207196</v>
       </c>
-      <c r="I42" s="16"/>
+      <c r="I42" s="16">
+        <v>391</v>
+      </c>
       <c r="J42" s="12"/>
       <c r="K42" s="12"/>
-      <c r="L42" s="16"/>
+      <c r="L42" s="16">
+        <v>449</v>
+      </c>
       <c r="M42" s="12"/>
       <c r="N42" s="12"/>
       <c r="O42" s="12"/>
       <c r="P42" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="43" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5335,7 +5413,7 @@
       <c r="E43" s="8" t="s">
         <v>95</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="22">
         <v>4080000</v>
       </c>
       <c r="G43" s="9">
@@ -5344,15 +5422,19 @@
       <c r="H43" s="9">
         <v>652127196</v>
       </c>
-      <c r="I43" s="12"/>
+      <c r="I43" s="16">
+        <v>385</v>
+      </c>
       <c r="J43" s="12"/>
       <c r="K43" s="12"/>
-      <c r="L43" s="12"/>
+      <c r="L43" s="16">
+        <v>443</v>
+      </c>
       <c r="M43" s="12"/>
       <c r="N43" s="12"/>
       <c r="O43" s="12"/>
       <c r="P43" s="17" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
     </row>
     <row r="44" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5374,7 +5456,7 @@
       <c r="F44" s="9">
         <v>0</v>
       </c>
-      <c r="G44" s="19">
+      <c r="G44" s="22">
         <v>104000000</v>
       </c>
       <c r="H44" s="9">
@@ -5382,7 +5464,9 @@
       </c>
       <c r="I44" s="12"/>
       <c r="J44" s="12"/>
-      <c r="K44" s="18"/>
+      <c r="K44" s="16">
+        <v>277</v>
+      </c>
       <c r="L44" s="12"/>
       <c r="M44" s="12"/>
       <c r="N44" s="12"/>
@@ -5405,7 +5489,7 @@
       <c r="E45" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="26">
         <v>670000</v>
       </c>
       <c r="G45" s="9">
@@ -5414,15 +5498,19 @@
       <c r="H45" s="9">
         <v>755457196</v>
       </c>
-      <c r="I45" s="12"/>
+      <c r="I45" s="25">
+        <v>380</v>
+      </c>
       <c r="J45" s="12"/>
       <c r="K45" s="12"/>
-      <c r="L45" s="12"/>
+      <c r="L45" s="25">
+        <v>438</v>
+      </c>
       <c r="M45" s="12"/>
       <c r="N45" s="12"/>
       <c r="O45" s="12"/>
-      <c r="P45" s="17" t="s">
-        <v>207</v>
+      <c r="P45" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="46" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5441,7 +5529,7 @@
       <c r="E46" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="26">
         <v>1000000</v>
       </c>
       <c r="G46" s="9">
@@ -5450,15 +5538,19 @@
       <c r="H46" s="9">
         <v>754457196</v>
       </c>
-      <c r="I46" s="12"/>
+      <c r="I46" s="25">
+        <v>380</v>
+      </c>
       <c r="J46" s="12"/>
       <c r="K46" s="12"/>
-      <c r="L46" s="12"/>
+      <c r="L46" s="25">
+        <v>438</v>
+      </c>
       <c r="M46" s="12"/>
       <c r="N46" s="12"/>
       <c r="O46" s="12"/>
-      <c r="P46" s="17" t="s">
-        <v>207</v>
+      <c r="P46" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="47" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5477,7 +5569,7 @@
       <c r="E47" s="8" t="s">
         <v>104</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="26">
         <v>7750000</v>
       </c>
       <c r="G47" s="9">
@@ -5486,15 +5578,19 @@
       <c r="H47" s="9">
         <v>746707196</v>
       </c>
-      <c r="I47" s="12"/>
+      <c r="I47" s="25">
+        <v>380</v>
+      </c>
       <c r="J47" s="12"/>
       <c r="K47" s="12"/>
-      <c r="L47" s="12"/>
+      <c r="L47" s="25">
+        <v>438</v>
+      </c>
       <c r="M47" s="12"/>
       <c r="N47" s="12"/>
       <c r="O47" s="12"/>
-      <c r="P47" s="17" t="s">
-        <v>207</v>
+      <c r="P47" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="48" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5513,7 +5609,7 @@
       <c r="E48" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="26">
         <v>1230000</v>
       </c>
       <c r="G48" s="9">
@@ -5522,15 +5618,19 @@
       <c r="H48" s="9">
         <v>745477196</v>
       </c>
-      <c r="I48" s="12"/>
+      <c r="I48" s="25">
+        <v>380</v>
+      </c>
       <c r="J48" s="12"/>
       <c r="K48" s="12"/>
-      <c r="L48" s="12"/>
+      <c r="L48" s="25">
+        <v>438</v>
+      </c>
       <c r="M48" s="12"/>
       <c r="N48" s="12"/>
       <c r="O48" s="12"/>
-      <c r="P48" s="17" t="s">
-        <v>207</v>
+      <c r="P48" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="49" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5549,7 +5649,7 @@
       <c r="E49" s="8" t="s">
         <v>108</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F49" s="26">
         <v>19085000</v>
       </c>
       <c r="G49" s="9">
@@ -5558,15 +5658,19 @@
       <c r="H49" s="9">
         <v>726392196</v>
       </c>
-      <c r="I49" s="12"/>
+      <c r="I49" s="25">
+        <v>380</v>
+      </c>
       <c r="J49" s="12"/>
       <c r="K49" s="12"/>
-      <c r="L49" s="12"/>
+      <c r="L49" s="25">
+        <v>438</v>
+      </c>
       <c r="M49" s="12"/>
       <c r="N49" s="12"/>
       <c r="O49" s="12"/>
-      <c r="P49" s="17" t="s">
-        <v>207</v>
+      <c r="P49" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="50" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5585,7 +5689,7 @@
       <c r="E50" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="22">
         <v>11000</v>
       </c>
       <c r="G50" s="9">
@@ -5598,8 +5702,12 @@
       <c r="J50" s="12"/>
       <c r="K50" s="12"/>
       <c r="L50" s="12"/>
-      <c r="M50" s="16"/>
-      <c r="N50" s="16"/>
+      <c r="M50" s="16">
+        <v>390</v>
+      </c>
+      <c r="N50" s="16">
+        <v>448</v>
+      </c>
       <c r="O50" s="16">
         <v>11000</v>
       </c>
@@ -5621,7 +5729,7 @@
       <c r="E51" s="8" t="s">
         <v>110</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F51" s="22">
         <v>2620000</v>
       </c>
       <c r="G51" s="9">
@@ -5630,14 +5738,20 @@
       <c r="H51" s="9">
         <v>723761196</v>
       </c>
-      <c r="I51" s="12"/>
+      <c r="I51" s="16">
+        <v>386</v>
+      </c>
       <c r="J51" s="12"/>
       <c r="K51" s="12"/>
-      <c r="L51" s="12"/>
+      <c r="L51" s="16">
+        <v>444</v>
+      </c>
       <c r="M51" s="12"/>
       <c r="N51" s="12"/>
       <c r="O51" s="12"/>
-      <c r="P51" s="12"/>
+      <c r="P51" s="17" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="52" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A52" s="8">
@@ -5655,7 +5769,7 @@
       <c r="E52" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="26">
         <v>2000000</v>
       </c>
       <c r="G52" s="9">
@@ -5664,15 +5778,19 @@
       <c r="H52" s="9">
         <v>721761196</v>
       </c>
-      <c r="I52" s="12"/>
+      <c r="I52" s="25">
+        <v>380</v>
+      </c>
       <c r="J52" s="12"/>
       <c r="K52" s="12"/>
-      <c r="L52" s="12"/>
+      <c r="L52" s="25">
+        <v>438</v>
+      </c>
       <c r="M52" s="12"/>
       <c r="N52" s="12"/>
       <c r="O52" s="12"/>
-      <c r="P52" s="17" t="s">
-        <v>207</v>
+      <c r="P52" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="53" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5691,7 +5809,7 @@
       <c r="E53" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="26">
         <v>10220000</v>
       </c>
       <c r="G53" s="9">
@@ -5700,15 +5818,19 @@
       <c r="H53" s="9">
         <v>711541196</v>
       </c>
-      <c r="I53" s="12"/>
+      <c r="I53" s="25">
+        <v>380</v>
+      </c>
       <c r="J53" s="12"/>
       <c r="K53" s="12"/>
-      <c r="L53" s="12"/>
+      <c r="L53" s="25">
+        <v>438</v>
+      </c>
       <c r="M53" s="12"/>
       <c r="N53" s="12"/>
       <c r="O53" s="12"/>
-      <c r="P53" s="17" t="s">
-        <v>207</v>
+      <c r="P53" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="54" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5727,7 +5849,7 @@
       <c r="E54" s="8" t="s">
         <v>117</v>
       </c>
-      <c r="F54" s="9">
+      <c r="F54" s="26">
         <v>2720000</v>
       </c>
       <c r="G54" s="9">
@@ -5736,15 +5858,19 @@
       <c r="H54" s="9">
         <v>708821196</v>
       </c>
-      <c r="I54" s="12"/>
+      <c r="I54" s="25">
+        <v>380</v>
+      </c>
       <c r="J54" s="12"/>
       <c r="K54" s="12"/>
-      <c r="L54" s="12"/>
+      <c r="L54" s="25">
+        <v>438</v>
+      </c>
       <c r="M54" s="12"/>
       <c r="N54" s="12"/>
       <c r="O54" s="12"/>
-      <c r="P54" s="17" t="s">
-        <v>207</v>
+      <c r="P54" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="55" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5763,7 +5889,7 @@
       <c r="E55" s="8" t="s">
         <v>119</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="26">
         <v>1090000</v>
       </c>
       <c r="G55" s="9">
@@ -5772,15 +5898,19 @@
       <c r="H55" s="9">
         <v>707731196</v>
       </c>
-      <c r="I55" s="12"/>
+      <c r="I55" s="25">
+        <v>380</v>
+      </c>
       <c r="J55" s="12"/>
       <c r="K55" s="12"/>
-      <c r="L55" s="12"/>
+      <c r="L55" s="25">
+        <v>438</v>
+      </c>
       <c r="M55" s="12"/>
       <c r="N55" s="12"/>
       <c r="O55" s="12"/>
-      <c r="P55" s="17" t="s">
-        <v>207</v>
+      <c r="P55" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="56" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5799,7 +5929,7 @@
       <c r="E56" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56" s="22">
         <v>60000</v>
       </c>
       <c r="G56" s="9">
@@ -5812,8 +5942,12 @@
       <c r="J56" s="12"/>
       <c r="K56" s="12"/>
       <c r="L56" s="12"/>
-      <c r="M56" s="16"/>
-      <c r="N56" s="16"/>
+      <c r="M56" s="16">
+        <v>390</v>
+      </c>
+      <c r="N56" s="16">
+        <v>448</v>
+      </c>
       <c r="O56" s="16">
         <v>60000</v>
       </c>
@@ -5835,7 +5969,7 @@
       <c r="E57" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F57" s="22">
         <v>150000000</v>
       </c>
       <c r="G57" s="9">
@@ -5844,15 +5978,19 @@
       <c r="H57" s="9">
         <v>557671196</v>
       </c>
-      <c r="I57" s="12"/>
+      <c r="I57" s="16">
+        <v>387</v>
+      </c>
       <c r="J57" s="12"/>
       <c r="K57" s="12"/>
-      <c r="L57" s="12"/>
+      <c r="L57" s="16">
+        <v>445</v>
+      </c>
       <c r="M57" s="12"/>
       <c r="N57" s="12"/>
       <c r="O57" s="12"/>
       <c r="P57" s="17" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5871,7 +6009,7 @@
       <c r="E58" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="F58" s="9">
+      <c r="F58" s="26">
         <v>2500000</v>
       </c>
       <c r="G58" s="9">
@@ -5880,15 +6018,19 @@
       <c r="H58" s="9">
         <v>555171196</v>
       </c>
-      <c r="I58" s="12"/>
+      <c r="I58" s="25">
+        <v>380</v>
+      </c>
       <c r="J58" s="12"/>
       <c r="K58" s="12"/>
-      <c r="L58" s="12"/>
+      <c r="L58" s="25">
+        <v>438</v>
+      </c>
       <c r="M58" s="12"/>
       <c r="N58" s="12"/>
       <c r="O58" s="12"/>
-      <c r="P58" s="17" t="s">
-        <v>207</v>
+      <c r="P58" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="59" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5907,7 +6049,7 @@
       <c r="E59" s="8" t="s">
         <v>125</v>
       </c>
-      <c r="F59" s="9">
+      <c r="F59" s="26">
         <v>1070000</v>
       </c>
       <c r="G59" s="9">
@@ -5916,15 +6058,19 @@
       <c r="H59" s="9">
         <v>554101196</v>
       </c>
-      <c r="I59" s="12"/>
+      <c r="I59" s="25">
+        <v>380</v>
+      </c>
       <c r="J59" s="12"/>
       <c r="K59" s="12"/>
-      <c r="L59" s="12"/>
+      <c r="L59" s="25">
+        <v>438</v>
+      </c>
       <c r="M59" s="12"/>
       <c r="N59" s="12"/>
       <c r="O59" s="12"/>
-      <c r="P59" s="17" t="s">
-        <v>207</v>
+      <c r="P59" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="60" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5943,7 +6089,7 @@
       <c r="E60" s="8" t="s">
         <v>127</v>
       </c>
-      <c r="F60" s="9">
+      <c r="F60" s="26">
         <v>9620000</v>
       </c>
       <c r="G60" s="9">
@@ -5952,15 +6098,19 @@
       <c r="H60" s="9">
         <v>544481196</v>
       </c>
-      <c r="I60" s="12"/>
+      <c r="I60" s="25">
+        <v>380</v>
+      </c>
       <c r="J60" s="12"/>
       <c r="K60" s="12"/>
-      <c r="L60" s="12"/>
+      <c r="L60" s="25">
+        <v>438</v>
+      </c>
       <c r="M60" s="12"/>
       <c r="N60" s="12"/>
       <c r="O60" s="12"/>
-      <c r="P60" s="17" t="s">
-        <v>207</v>
+      <c r="P60" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="61" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -5979,7 +6129,7 @@
       <c r="E61" s="8" t="s">
         <v>129</v>
       </c>
-      <c r="F61" s="9">
+      <c r="F61" s="26">
         <v>1270000</v>
       </c>
       <c r="G61" s="9">
@@ -5988,15 +6138,19 @@
       <c r="H61" s="9">
         <v>543211196</v>
       </c>
-      <c r="I61" s="12"/>
+      <c r="I61" s="25">
+        <v>380</v>
+      </c>
       <c r="J61" s="12"/>
       <c r="K61" s="12"/>
-      <c r="L61" s="12"/>
+      <c r="L61" s="25">
+        <v>438</v>
+      </c>
       <c r="M61" s="12"/>
       <c r="N61" s="12"/>
       <c r="O61" s="12"/>
-      <c r="P61" s="17" t="s">
-        <v>207</v>
+      <c r="P61" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="62" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6015,7 +6169,7 @@
       <c r="E62" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="F62" s="9">
+      <c r="F62" s="26">
         <v>1500000</v>
       </c>
       <c r="G62" s="9">
@@ -6024,15 +6178,19 @@
       <c r="H62" s="9">
         <v>541711196</v>
       </c>
-      <c r="I62" s="12"/>
+      <c r="I62" s="25">
+        <v>380</v>
+      </c>
       <c r="J62" s="12"/>
       <c r="K62" s="12"/>
-      <c r="L62" s="12"/>
+      <c r="L62" s="25">
+        <v>438</v>
+      </c>
       <c r="M62" s="12"/>
       <c r="N62" s="12"/>
       <c r="O62" s="12"/>
-      <c r="P62" s="17" t="s">
-        <v>207</v>
+      <c r="P62" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="63" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6051,7 +6209,7 @@
       <c r="E63" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="F63" s="9">
+      <c r="F63" s="26">
         <v>1040000</v>
       </c>
       <c r="G63" s="9">
@@ -6060,15 +6218,19 @@
       <c r="H63" s="9">
         <v>540671196</v>
       </c>
-      <c r="I63" s="12"/>
+      <c r="I63" s="25">
+        <v>380</v>
+      </c>
       <c r="J63" s="12"/>
       <c r="K63" s="12"/>
-      <c r="L63" s="12"/>
+      <c r="L63" s="25">
+        <v>438</v>
+      </c>
       <c r="M63" s="12"/>
       <c r="N63" s="12"/>
       <c r="O63" s="12"/>
-      <c r="P63" s="17" t="s">
-        <v>207</v>
+      <c r="P63" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="64" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6087,7 +6249,7 @@
       <c r="E64" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F64" s="9">
+      <c r="F64" s="22">
         <v>11000</v>
       </c>
       <c r="G64" s="9">
@@ -6100,8 +6262,12 @@
       <c r="J64" s="12"/>
       <c r="K64" s="12"/>
       <c r="L64" s="12"/>
-      <c r="M64" s="16"/>
-      <c r="N64" s="16"/>
+      <c r="M64" s="16">
+        <v>390</v>
+      </c>
+      <c r="N64" s="16">
+        <v>448</v>
+      </c>
       <c r="O64" s="16">
         <v>11000</v>
       </c>
@@ -6123,7 +6289,7 @@
       <c r="E65" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="F65" s="9">
+      <c r="F65" s="22">
         <v>2381000</v>
       </c>
       <c r="G65" s="9">
@@ -6132,10 +6298,14 @@
       <c r="H65" s="9">
         <v>538279196</v>
       </c>
-      <c r="I65" s="12"/>
+      <c r="I65" s="16">
+        <v>388</v>
+      </c>
       <c r="J65" s="12"/>
       <c r="K65" s="12"/>
-      <c r="L65" s="12"/>
+      <c r="L65" s="16">
+        <v>446</v>
+      </c>
       <c r="M65" s="12"/>
       <c r="N65" s="12"/>
       <c r="O65" s="12"/>
@@ -6159,7 +6329,7 @@
       <c r="E66" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="F66" s="9">
+      <c r="F66" s="26">
         <v>7500000</v>
       </c>
       <c r="G66" s="9">
@@ -6168,15 +6338,19 @@
       <c r="H66" s="9">
         <v>530779196</v>
       </c>
-      <c r="I66" s="12"/>
+      <c r="I66" s="25">
+        <v>380</v>
+      </c>
       <c r="J66" s="12"/>
       <c r="K66" s="12"/>
-      <c r="L66" s="12"/>
+      <c r="L66" s="25">
+        <v>438</v>
+      </c>
       <c r="M66" s="12"/>
       <c r="N66" s="12"/>
       <c r="O66" s="12"/>
-      <c r="P66" s="17" t="s">
-        <v>207</v>
+      <c r="P66" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="67" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6195,7 +6369,7 @@
       <c r="E67" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="F67" s="9">
+      <c r="F67" s="26">
         <v>1700000</v>
       </c>
       <c r="G67" s="9">
@@ -6204,15 +6378,19 @@
       <c r="H67" s="9">
         <v>529079196</v>
       </c>
-      <c r="I67" s="12"/>
+      <c r="I67" s="25">
+        <v>380</v>
+      </c>
       <c r="J67" s="12"/>
       <c r="K67" s="12"/>
-      <c r="L67" s="12"/>
+      <c r="L67" s="25">
+        <v>438</v>
+      </c>
       <c r="M67" s="12"/>
       <c r="N67" s="12"/>
       <c r="O67" s="12"/>
-      <c r="P67" s="17" t="s">
-        <v>207</v>
+      <c r="P67" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="68" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6231,7 +6409,7 @@
       <c r="E68" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="F68" s="9">
+      <c r="F68" s="26">
         <v>2330000</v>
       </c>
       <c r="G68" s="9">
@@ -6240,15 +6418,19 @@
       <c r="H68" s="9">
         <v>526749196</v>
       </c>
-      <c r="I68" s="12"/>
+      <c r="I68" s="25">
+        <v>380</v>
+      </c>
       <c r="J68" s="12"/>
       <c r="K68" s="12"/>
-      <c r="L68" s="12"/>
+      <c r="L68" s="25">
+        <v>438</v>
+      </c>
       <c r="M68" s="12"/>
       <c r="N68" s="12"/>
       <c r="O68" s="12"/>
-      <c r="P68" s="17" t="s">
-        <v>207</v>
+      <c r="P68" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="69" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6267,7 +6449,7 @@
       <c r="E69" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="F69" s="9">
+      <c r="F69" s="26">
         <v>5590000</v>
       </c>
       <c r="G69" s="9">
@@ -6276,15 +6458,19 @@
       <c r="H69" s="9">
         <v>521159196</v>
       </c>
-      <c r="I69" s="12"/>
+      <c r="I69" s="25">
+        <v>380</v>
+      </c>
       <c r="J69" s="12"/>
       <c r="K69" s="12"/>
-      <c r="L69" s="12"/>
+      <c r="L69" s="25">
+        <v>438</v>
+      </c>
       <c r="M69" s="12"/>
       <c r="N69" s="12"/>
       <c r="O69" s="12"/>
-      <c r="P69" s="17" t="s">
-        <v>207</v>
+      <c r="P69" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="70" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6303,7 +6489,7 @@
       <c r="E70" s="8" t="s">
         <v>146</v>
       </c>
-      <c r="F70" s="9">
+      <c r="F70" s="26">
         <v>1050000</v>
       </c>
       <c r="G70" s="9">
@@ -6312,15 +6498,19 @@
       <c r="H70" s="9">
         <v>520109196</v>
       </c>
-      <c r="I70" s="12"/>
+      <c r="I70" s="25">
+        <v>380</v>
+      </c>
       <c r="J70" s="12"/>
       <c r="K70" s="12"/>
-      <c r="L70" s="12"/>
+      <c r="L70" s="25">
+        <v>438</v>
+      </c>
       <c r="M70" s="12"/>
       <c r="N70" s="12"/>
       <c r="O70" s="12"/>
-      <c r="P70" s="17" t="s">
-        <v>207</v>
+      <c r="P70" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="71" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6339,7 +6529,7 @@
       <c r="E71" s="8" t="s">
         <v>148</v>
       </c>
-      <c r="F71" s="9">
+      <c r="F71" s="26">
         <v>700000</v>
       </c>
       <c r="G71" s="9">
@@ -6348,15 +6538,19 @@
       <c r="H71" s="9">
         <v>519409196</v>
       </c>
-      <c r="I71" s="12"/>
+      <c r="I71" s="25">
+        <v>380</v>
+      </c>
       <c r="J71" s="12"/>
       <c r="K71" s="12"/>
-      <c r="L71" s="12"/>
+      <c r="L71" s="25">
+        <v>438</v>
+      </c>
       <c r="M71" s="12"/>
       <c r="N71" s="12"/>
       <c r="O71" s="12"/>
-      <c r="P71" s="17" t="s">
-        <v>207</v>
+      <c r="P71" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="72" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6375,7 +6569,7 @@
       <c r="E72" s="8" t="s">
         <v>151</v>
       </c>
-      <c r="F72" s="9">
+      <c r="F72" s="26">
         <v>1170000</v>
       </c>
       <c r="G72" s="9">
@@ -6384,15 +6578,19 @@
       <c r="H72" s="9">
         <v>518239196</v>
       </c>
-      <c r="I72" s="12"/>
+      <c r="I72" s="25">
+        <v>380</v>
+      </c>
       <c r="J72" s="12"/>
       <c r="K72" s="12"/>
-      <c r="L72" s="12"/>
+      <c r="L72" s="25">
+        <v>438</v>
+      </c>
       <c r="M72" s="12"/>
       <c r="N72" s="12"/>
       <c r="O72" s="12"/>
-      <c r="P72" s="17" t="s">
-        <v>207</v>
+      <c r="P72" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="73" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6411,7 +6609,7 @@
       <c r="E73" s="8" t="s">
         <v>153</v>
       </c>
-      <c r="F73" s="9">
+      <c r="F73" s="26">
         <v>2520000</v>
       </c>
       <c r="G73" s="9">
@@ -6420,15 +6618,19 @@
       <c r="H73" s="9">
         <v>515719196</v>
       </c>
-      <c r="I73" s="12"/>
+      <c r="I73" s="25">
+        <v>380</v>
+      </c>
       <c r="J73" s="12"/>
       <c r="K73" s="12"/>
-      <c r="L73" s="12"/>
+      <c r="L73" s="25">
+        <v>438</v>
+      </c>
       <c r="M73" s="12"/>
       <c r="N73" s="12"/>
       <c r="O73" s="12"/>
-      <c r="P73" s="17" t="s">
-        <v>207</v>
+      <c r="P73" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="74" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6447,7 +6649,7 @@
       <c r="E74" s="8" t="s">
         <v>155</v>
       </c>
-      <c r="F74" s="9">
+      <c r="F74" s="26">
         <v>1730000</v>
       </c>
       <c r="G74" s="9">
@@ -6456,15 +6658,19 @@
       <c r="H74" s="9">
         <v>513989196</v>
       </c>
-      <c r="I74" s="12"/>
+      <c r="I74" s="25">
+        <v>380</v>
+      </c>
       <c r="J74" s="12"/>
       <c r="K74" s="12"/>
-      <c r="L74" s="12"/>
+      <c r="L74" s="25">
+        <v>438</v>
+      </c>
       <c r="M74" s="12"/>
       <c r="N74" s="12"/>
       <c r="O74" s="12"/>
-      <c r="P74" s="17" t="s">
-        <v>207</v>
+      <c r="P74" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="75" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6483,7 +6689,7 @@
       <c r="E75" s="8" t="s">
         <v>158</v>
       </c>
-      <c r="F75" s="9">
+      <c r="F75" s="26">
         <v>1760000</v>
       </c>
       <c r="G75" s="9">
@@ -6492,15 +6698,19 @@
       <c r="H75" s="9">
         <v>512229196</v>
       </c>
-      <c r="I75" s="12"/>
+      <c r="I75" s="25">
+        <v>380</v>
+      </c>
       <c r="J75" s="12"/>
       <c r="K75" s="12"/>
-      <c r="L75" s="12"/>
+      <c r="L75" s="25">
+        <v>438</v>
+      </c>
       <c r="M75" s="12"/>
       <c r="N75" s="12"/>
       <c r="O75" s="12"/>
-      <c r="P75" s="17" t="s">
-        <v>207</v>
+      <c r="P75" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="76" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6519,7 +6729,7 @@
       <c r="E76" s="8" t="s">
         <v>160</v>
       </c>
-      <c r="F76" s="9">
+      <c r="F76" s="26">
         <v>2000000</v>
       </c>
       <c r="G76" s="9">
@@ -6528,15 +6738,19 @@
       <c r="H76" s="9">
         <v>510229196</v>
       </c>
-      <c r="I76" s="12"/>
+      <c r="I76" s="25">
+        <v>380</v>
+      </c>
       <c r="J76" s="12"/>
       <c r="K76" s="12"/>
-      <c r="L76" s="12"/>
+      <c r="L76" s="25">
+        <v>438</v>
+      </c>
       <c r="M76" s="12"/>
       <c r="N76" s="12"/>
       <c r="O76" s="12"/>
-      <c r="P76" s="17" t="s">
-        <v>207</v>
+      <c r="P76" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="77" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6555,7 +6769,7 @@
       <c r="E77" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77" s="26">
         <v>1450000</v>
       </c>
       <c r="G77" s="9">
@@ -6564,15 +6778,19 @@
       <c r="H77" s="9">
         <v>508779196</v>
       </c>
-      <c r="I77" s="12"/>
+      <c r="I77" s="25">
+        <v>380</v>
+      </c>
       <c r="J77" s="12"/>
       <c r="K77" s="12"/>
-      <c r="L77" s="12"/>
+      <c r="L77" s="25">
+        <v>438</v>
+      </c>
       <c r="M77" s="12"/>
       <c r="N77" s="12"/>
       <c r="O77" s="12"/>
-      <c r="P77" s="17" t="s">
-        <v>207</v>
+      <c r="P77" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="78" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6591,7 +6809,7 @@
       <c r="E78" s="8" t="s">
         <v>165</v>
       </c>
-      <c r="F78" s="9">
+      <c r="F78" s="26">
         <v>1030000</v>
       </c>
       <c r="G78" s="9">
@@ -6600,15 +6818,19 @@
       <c r="H78" s="9">
         <v>507749196</v>
       </c>
-      <c r="I78" s="12"/>
+      <c r="I78" s="25">
+        <v>380</v>
+      </c>
       <c r="J78" s="12"/>
       <c r="K78" s="12"/>
-      <c r="L78" s="12"/>
+      <c r="L78" s="25">
+        <v>438</v>
+      </c>
       <c r="M78" s="12"/>
       <c r="N78" s="12"/>
       <c r="O78" s="12"/>
-      <c r="P78" s="17" t="s">
-        <v>207</v>
+      <c r="P78" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="79" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6627,7 +6849,7 @@
       <c r="E79" s="8" t="s">
         <v>167</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79" s="26">
         <v>1060000</v>
       </c>
       <c r="G79" s="9">
@@ -6636,15 +6858,19 @@
       <c r="H79" s="9">
         <v>506689196</v>
       </c>
-      <c r="I79" s="12"/>
+      <c r="I79" s="25">
+        <v>380</v>
+      </c>
       <c r="J79" s="12"/>
       <c r="K79" s="12"/>
-      <c r="L79" s="12"/>
+      <c r="L79" s="25">
+        <v>438</v>
+      </c>
       <c r="M79" s="12"/>
       <c r="N79" s="12"/>
       <c r="O79" s="12"/>
-      <c r="P79" s="17" t="s">
-        <v>207</v>
+      <c r="P79" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="80" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6663,7 +6889,7 @@
       <c r="E80" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="F80" s="9">
+      <c r="F80" s="26">
         <v>350000</v>
       </c>
       <c r="G80" s="9">
@@ -6672,15 +6898,19 @@
       <c r="H80" s="9">
         <v>506339196</v>
       </c>
-      <c r="I80" s="12"/>
+      <c r="I80" s="25">
+        <v>380</v>
+      </c>
       <c r="J80" s="12"/>
       <c r="K80" s="12"/>
-      <c r="L80" s="12"/>
+      <c r="L80" s="25">
+        <v>438</v>
+      </c>
       <c r="M80" s="12"/>
       <c r="N80" s="12"/>
       <c r="O80" s="12"/>
-      <c r="P80" s="17" t="s">
-        <v>207</v>
+      <c r="P80" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="81" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6699,7 +6929,7 @@
       <c r="E81" s="8" t="s">
         <v>171</v>
       </c>
-      <c r="F81" s="9">
+      <c r="F81" s="26">
         <v>1300000</v>
       </c>
       <c r="G81" s="9">
@@ -6708,15 +6938,19 @@
       <c r="H81" s="9">
         <v>505039196</v>
       </c>
-      <c r="I81" s="12"/>
+      <c r="I81" s="25">
+        <v>380</v>
+      </c>
       <c r="J81" s="12"/>
       <c r="K81" s="12"/>
-      <c r="L81" s="12"/>
+      <c r="L81" s="25">
+        <v>438</v>
+      </c>
       <c r="M81" s="12"/>
       <c r="N81" s="12"/>
       <c r="O81" s="12"/>
-      <c r="P81" s="17" t="s">
-        <v>207</v>
+      <c r="P81" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="82" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6735,7 +6969,7 @@
       <c r="E82" s="8" t="s">
         <v>173</v>
       </c>
-      <c r="F82" s="9">
+      <c r="F82" s="26">
         <v>240000</v>
       </c>
       <c r="G82" s="9">
@@ -6744,15 +6978,19 @@
       <c r="H82" s="9">
         <v>504799196</v>
       </c>
-      <c r="I82" s="12"/>
+      <c r="I82" s="25">
+        <v>380</v>
+      </c>
       <c r="J82" s="12"/>
       <c r="K82" s="12"/>
-      <c r="L82" s="12"/>
+      <c r="L82" s="25">
+        <v>438</v>
+      </c>
       <c r="M82" s="12"/>
       <c r="N82" s="12"/>
       <c r="O82" s="12"/>
-      <c r="P82" s="17" t="s">
-        <v>207</v>
+      <c r="P82" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="83" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6771,7 +7009,7 @@
       <c r="E83" s="8" t="s">
         <v>175</v>
       </c>
-      <c r="F83" s="9">
+      <c r="F83" s="26">
         <v>2540000</v>
       </c>
       <c r="G83" s="9">
@@ -6780,15 +7018,19 @@
       <c r="H83" s="9">
         <v>502259196</v>
       </c>
-      <c r="I83" s="12"/>
+      <c r="I83" s="25">
+        <v>380</v>
+      </c>
       <c r="J83" s="12"/>
       <c r="K83" s="12"/>
-      <c r="L83" s="12"/>
+      <c r="L83" s="25">
+        <v>438</v>
+      </c>
       <c r="M83" s="12"/>
       <c r="N83" s="12"/>
       <c r="O83" s="12"/>
-      <c r="P83" s="17" t="s">
-        <v>207</v>
+      <c r="P83" s="25" t="s">
+        <v>204</v>
       </c>
     </row>
     <row r="84" spans="1:16" ht="24.75" customHeight="1" x14ac:dyDescent="0.15">
@@ -6807,7 +7049,7 @@
       <c r="E84" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="F84" s="9">
+      <c r="F84" s="22">
         <v>25000</v>
       </c>
       <c r="G84" s="9">
@@ -6820,8 +7062,12 @@
       <c r="J84" s="12"/>
       <c r="K84" s="12"/>
       <c r="L84" s="12"/>
-      <c r="M84" s="16"/>
-      <c r="N84" s="16"/>
+      <c r="M84" s="16">
+        <v>390</v>
+      </c>
+      <c r="N84" s="16">
+        <v>448</v>
+      </c>
       <c r="O84" s="16">
         <v>25000</v>
       </c>
@@ -6843,7 +7089,7 @@
       <c r="E85" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="F85" s="9">
+      <c r="F85" s="22">
         <v>50000000</v>
       </c>
       <c r="G85" s="9">
@@ -6852,10 +7098,14 @@
       <c r="H85" s="9">
         <v>452234196</v>
       </c>
-      <c r="I85" s="12"/>
+      <c r="I85" s="16">
+        <v>389</v>
+      </c>
       <c r="J85" s="12"/>
       <c r="K85" s="12"/>
-      <c r="L85" s="12"/>
+      <c r="L85" s="16">
+        <v>447</v>
+      </c>
       <c r="M85" s="12"/>
       <c r="N85" s="12"/>
       <c r="O85" s="12"/>
@@ -6864,6 +7114,7 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P85" xr:uid="{B228B652-FBEA-4CAE-A130-90FBF627410B}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>